--- a/Outcome/Appendix/figure_data/fig10.xlsx
+++ b/Outcome/Appendix/figure_data/fig10.xlsx
@@ -8501,19 +8501,19 @@
         <v>43831</v>
       </c>
       <c r="B194" t="n">
-        <v>3.48922945921719</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C194" t="n">
-        <v>0.281822706792655</v>
+        <v>1.35150455359448</v>
       </c>
       <c r="D194" t="n">
-        <v>0.163486298696979</v>
+        <v>0.8508760771789</v>
       </c>
       <c r="E194" t="n">
-        <v>8.79581346188835</v>
+        <v>7.76299343213201</v>
       </c>
       <c r="F194" t="n">
-        <v>12.5595993338432</v>
+        <v>12.3304923648059</v>
       </c>
       <c r="G194" t="s">
         <v>68</v>
@@ -8528,7 +8528,7 @@
         <v>14</v>
       </c>
       <c r="K194" t="n">
-        <v>349.923</v>
+        <v>324.909</v>
       </c>
       <c r="L194" t="s">
         <v>41</v>
@@ -8542,19 +8542,19 @@
         <v>43862</v>
       </c>
       <c r="B195" t="n">
-        <v>3.44238856210644</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C195" t="n">
-        <v>0.278128347165597</v>
+        <v>1.34703374978168</v>
       </c>
       <c r="D195" t="n">
-        <v>0.16198062571128</v>
+        <v>0.846575113307784</v>
       </c>
       <c r="E195" t="n">
-        <v>8.72799788625267</v>
+        <v>7.78875880040192</v>
       </c>
       <c r="F195" t="n">
-        <v>12.4763898286817</v>
+        <v>12.3931365429071</v>
       </c>
       <c r="G195" t="s">
         <v>68</v>
@@ -8569,7 +8569,7 @@
         <v>14</v>
       </c>
       <c r="K195" t="n">
-        <v>1.718</v>
+        <v>1.616</v>
       </c>
       <c r="L195" t="s">
         <v>15</v>
@@ -8583,19 +8583,19 @@
         <v>43891</v>
       </c>
       <c r="B196" t="n">
-        <v>3.39566911443759</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C196" t="n">
-        <v>0.274519309758261</v>
+        <v>1.34259447299923</v>
       </c>
       <c r="D196" t="n">
-        <v>0.160496281174141</v>
+        <v>0.842311949144005</v>
       </c>
       <c r="E196" t="n">
-        <v>8.66046628674691</v>
+        <v>7.81451226267372</v>
       </c>
       <c r="F196" t="n">
-        <v>12.3935167555461</v>
+        <v>12.4558614937288</v>
       </c>
       <c r="G196" t="s">
         <v>68</v>
@@ -8610,7 +8610,7 @@
         <v>14</v>
       </c>
       <c r="K196" t="n">
-        <v>3.372</v>
+        <v>3.217</v>
       </c>
       <c r="L196" t="s">
         <v>15</v>
@@ -8624,19 +8624,19 @@
         <v>43922</v>
       </c>
       <c r="B197" t="n">
-        <v>3.34906636218101</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C197" t="n">
-        <v>0.270992400768374</v>
+        <v>1.33818632194869</v>
       </c>
       <c r="D197" t="n">
-        <v>0.159032802235213</v>
+        <v>0.838086053169818</v>
       </c>
       <c r="E197" t="n">
-        <v>8.59321818191257</v>
+        <v>7.84025423139295</v>
       </c>
       <c r="F197" t="n">
-        <v>12.3109801186087</v>
+        <v>12.5186679021427</v>
       </c>
       <c r="G197" t="s">
         <v>68</v>
@@ -8651,7 +8651,7 @@
         <v>69</v>
       </c>
       <c r="K197" t="n">
-        <v>0.67</v>
+        <v>0.649</v>
       </c>
       <c r="L197" t="s">
         <v>15</v>
@@ -8665,19 +8665,19 @@
         <v>43952</v>
       </c>
       <c r="B198" t="n">
-        <v>3.30257529901719</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C198" t="n">
-        <v>0.267544597631689</v>
+        <v>1.33380890310377</v>
       </c>
       <c r="D198" t="n">
-        <v>0.157589739814875</v>
+        <v>0.833896904655806</v>
       </c>
       <c r="E198" t="n">
-        <v>8.52625307922873</v>
+        <v>7.86598511123763</v>
       </c>
       <c r="F198" t="n">
-        <v>12.2287799060234</v>
+        <v>12.5815564423769</v>
       </c>
       <c r="G198" t="s">
         <v>68</v>
@@ -8692,7 +8692,7 @@
         <v>69</v>
       </c>
       <c r="K198" t="n">
-        <v>0.826</v>
+        <v>0.81</v>
       </c>
       <c r="L198" t="s">
         <v>15</v>
@@ -8706,19 +8706,19 @@
         <v>43983</v>
       </c>
       <c r="B199" t="n">
-        <v>3.25619064442641</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C199" t="n">
-        <v>0.264173036956965</v>
+        <v>1.3294618305059</v>
       </c>
       <c r="D199" t="n">
-        <v>0.156166658078871</v>
+        <v>0.82974399337001</v>
       </c>
       <c r="E199" t="n">
-        <v>8.45957047509405</v>
+        <v>7.89170529932253</v>
       </c>
       <c r="F199" t="n">
-        <v>12.1469160900321</v>
+        <v>12.644527778307</v>
       </c>
       <c r="G199" t="s">
         <v>68</v>
@@ -8733,7 +8733,7 @@
         <v>14</v>
       </c>
       <c r="K199" t="n">
-        <v>3.234</v>
+        <v>3.217</v>
       </c>
       <c r="L199" t="s">
         <v>15</v>
@@ -8747,19 +8747,19 @@
         <v>44013</v>
       </c>
       <c r="B200" t="n">
-        <v>3.20990681933038</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C200" t="n">
-        <v>0.260875003514185</v>
+        <v>1.32514472556671</v>
       </c>
       <c r="D200" t="n">
-        <v>0.154763133937613</v>
+        <v>0.825626819296882</v>
       </c>
       <c r="E200" t="n">
-        <v>8.39316985480523</v>
+        <v>7.91741518539687</v>
       </c>
       <c r="F200" t="n">
-        <v>12.0653886270698</v>
+        <v>12.7075825637367</v>
       </c>
       <c r="G200" t="s">
         <v>68</v>
@@ -8774,7 +8774,7 @@
         <v>69</v>
       </c>
       <c r="K200" t="n">
-        <v>0.536</v>
+        <v>0.541</v>
       </c>
       <c r="L200" t="s">
         <v>15</v>
@@ -8788,19 +8788,19 @@
         <v>44044</v>
       </c>
       <c r="B201" t="n">
-        <v>3.16371791894604</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C201" t="n">
-        <v>0.257647920166696</v>
+        <v>1.32085721687695</v>
       </c>
       <c r="D201" t="n">
-        <v>0.153378756568752</v>
+        <v>0.82154489236567</v>
       </c>
       <c r="E201" t="n">
-        <v>8.32705069253177</v>
+        <v>7.94311515203528</v>
       </c>
       <c r="F201" t="n">
-        <v>11.9841974578684</v>
+        <v>12.7707214426702</v>
       </c>
       <c r="G201" t="s">
         <v>68</v>
@@ -8815,7 +8815,7 @@
         <v>14</v>
       </c>
       <c r="K201" t="n">
-        <v>1.054</v>
+        <v>1.079</v>
       </c>
       <c r="L201" t="s">
         <v>15</v>
@@ -8829,19 +8829,19 @@
         <v>44075</v>
       </c>
       <c r="B202" t="n">
-        <v>3.11761768245465</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C202" t="n">
-        <v>0.254489338651032</v>
+        <v>1.31659894002169</v>
       </c>
       <c r="D202" t="n">
-        <v>0.152013126961745</v>
+        <v>0.817497732187837</v>
       </c>
       <c r="E202" t="n">
-        <v>8.26121245128703</v>
+        <v>7.96880557482266</v>
       </c>
       <c r="F202" t="n">
-        <v>11.9033425075605</v>
+        <v>12.8339450495744</v>
       </c>
       <c r="G202" t="s">
         <v>68</v>
@@ -8856,7 +8856,7 @@
         <v>69</v>
       </c>
       <c r="K202" t="n">
-        <v>0.446</v>
+        <v>0.463</v>
       </c>
       <c r="L202" t="s">
         <v>15</v>
@@ -8870,19 +8870,19 @@
         <v>44105</v>
       </c>
       <c r="B203" t="n">
-        <v>3.07159945902113</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C203" t="n">
-        <v>0.251396931119518</v>
+        <v>1.31236953740157</v>
       </c>
       <c r="D203" t="n">
-        <v>0.150665857483213</v>
+        <v>0.813484867803166</v>
       </c>
       <c r="E203" t="n">
-        <v>8.19565458289536</v>
+        <v>7.99448682253289</v>
       </c>
       <c r="F203" t="n">
-        <v>11.8228236857801</v>
+        <v>12.8972540096333</v>
       </c>
       <c r="G203" t="s">
         <v>68</v>
@@ -8897,7 +8897,7 @@
         <v>14</v>
       </c>
       <c r="K203" t="n">
-        <v>1.024</v>
+        <v>1.079</v>
       </c>
       <c r="L203" t="s">
         <v>15</v>
@@ -8911,19 +8911,19 @@
         <v>44136</v>
       </c>
       <c r="B204" t="n">
-        <v>3.0256561696166</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C204" t="n">
-        <v>0.248368482370595</v>
+        <v>1.30816865805979</v>
       </c>
       <c r="D204" t="n">
-        <v>0.149336571461953</v>
+        <v>0.809505837434201</v>
       </c>
       <c r="E204" t="n">
-        <v>8.13037652795517</v>
+        <v>8.02015925730189</v>
       </c>
       <c r="F204" t="n">
-        <v>11.7426408867635</v>
+        <v>12.9606489389933</v>
       </c>
       <c r="G204" t="s">
         <v>68</v>
@@ -8938,7 +8938,7 @@
         <v>14</v>
       </c>
       <c r="K204" t="n">
-        <v>303.566</v>
+        <v>324.909</v>
       </c>
       <c r="L204" t="s">
         <v>41</v>
@@ -8952,19 +8952,19 @@
         <v>44166</v>
       </c>
       <c r="B205" t="n">
-        <v>2.97978026399775</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C205" t="n">
-        <v>0.245401882700307</v>
+        <v>1.30399595751468</v>
       </c>
       <c r="D205" t="n">
-        <v>0.148024902792566</v>
+        <v>0.805560188248694</v>
       </c>
       <c r="E205" t="n">
-        <v>8.06537771579792</v>
+        <v>8.04582323479502</v>
       </c>
       <c r="F205" t="n">
-        <v>11.6627939894491</v>
+        <v>13.0241304450008</v>
       </c>
       <c r="G205" t="s">
         <v>68</v>
@@ -8979,7 +8979,7 @@
         <v>14</v>
       </c>
       <c r="K205" t="n">
-        <v>2.96</v>
+        <v>3.217</v>
       </c>
       <c r="L205" t="s">
         <v>15</v>
@@ -8993,19 +8993,19 @@
         <v>44197</v>
       </c>
       <c r="B206" t="n">
-        <v>2.93396367207645</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C206" t="n">
-        <v>0.242495121315874</v>
+        <v>1.29985109759761</v>
       </c>
       <c r="D206" t="n">
-        <v>0.146730495556683</v>
+        <v>0.801647476129748</v>
       </c>
       <c r="E206" t="n">
-        <v>8.00065756444276</v>
+        <v>8.07147910436919</v>
       </c>
       <c r="F206" t="n">
-        <v>11.5832828575748</v>
+        <v>13.0876991264329</v>
       </c>
       <c r="G206" t="s">
         <v>68</v>
@@ -9017,10 +9017,10 @@
         <v>0</v>
       </c>
       <c r="J206" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="K206" t="n">
-        <v>0.978</v>
+        <v>1.079</v>
       </c>
       <c r="L206" t="s">
         <v>15</v>
@@ -9034,19 +9034,19 @@
         <v>44228</v>
       </c>
       <c r="B207" t="n">
-        <v>2.88819774876559</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C207" t="n">
-        <v>0.239646280258731</v>
+        <v>1.29573374629598</v>
       </c>
       <c r="D207" t="n">
-        <v>0.145453003660886</v>
+        <v>0.79776726545335</v>
       </c>
       <c r="E207" t="n">
-        <v>7.93621548054673</v>
+        <v>8.0971272092298</v>
       </c>
       <c r="F207" t="n">
-        <v>11.5041073397756</v>
+        <v>13.1513555737189</v>
       </c>
       <c r="G207" t="s">
         <v>68</v>
@@ -9061,7 +9061,7 @@
         <v>14</v>
       </c>
       <c r="K207" t="n">
-        <v>1.442</v>
+        <v>1.616</v>
       </c>
       <c r="L207" t="s">
         <v>15</v>
@@ -9075,19 +9075,19 @@
         <v>44256</v>
       </c>
       <c r="B208" t="n">
-        <v>2.84247321120703</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C208" t="n">
-        <v>0.236853528790143</v>
+        <v>1.29164357760125</v>
       </c>
       <c r="D208" t="n">
-        <v>0.144192090490436</v>
+        <v>0.793919128873017</v>
       </c>
       <c r="E208" t="n">
-        <v>7.8720508593503</v>
+        <v>8.12276788658285</v>
       </c>
       <c r="F208" t="n">
-        <v>11.4252672696794</v>
+        <v>13.2151003691568</v>
       </c>
       <c r="G208" t="s">
         <v>68</v>
@@ -9102,7 +9102,7 @@
         <v>14</v>
       </c>
       <c r="K208" t="n">
-        <v>1.419</v>
+        <v>1.616</v>
       </c>
       <c r="L208" t="s">
         <v>15</v>
@@ -9116,19 +9116,19 @@
         <v>44287</v>
       </c>
       <c r="B209" t="n">
-        <v>2.79678006706433</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C209" t="n">
-        <v>0.234115118197476</v>
+        <v>1.28758027136163</v>
       </c>
       <c r="D209" t="n">
-        <v>0.142947428577988</v>
+        <v>0.790102647111275</v>
       </c>
       <c r="E209" t="n">
-        <v>7.80816308461822</v>
+        <v>8.14840146778213</v>
       </c>
       <c r="F209" t="n">
-        <v>11.3467624660016</v>
+        <v>13.278934087121</v>
       </c>
       <c r="G209" t="s">
         <v>68</v>
@@ -9143,7 +9143,7 @@
         <v>14</v>
       </c>
       <c r="K209" t="n">
-        <v>280.678</v>
+        <v>324.909</v>
       </c>
       <c r="L209" t="s">
         <v>41</v>
@@ -9157,19 +9157,19 @@
         <v>44317</v>
       </c>
       <c r="B210" t="n">
-        <v>2.75110753228643</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C210" t="n">
-        <v>0.231429376983595</v>
+        <v>1.28354351313936</v>
       </c>
       <c r="D210" t="n">
-        <v>0.14171869928653</v>
+        <v>0.786317408757711</v>
       </c>
       <c r="E210" t="n">
-        <v>7.74455152857531</v>
+        <v>8.17402827847197</v>
       </c>
       <c r="F210" t="n">
-        <v>11.2685927326389</v>
+        <v>13.3428572942651</v>
       </c>
       <c r="G210" t="s">
         <v>68</v>
@@ -9184,7 +9184,7 @@
         <v>14</v>
       </c>
       <c r="K210" t="n">
-        <v>1.374</v>
+        <v>1.616</v>
       </c>
       <c r="L210" t="s">
         <v>15</v>
@@ -9198,19 +9198,19 @@
         <v>44348</v>
       </c>
       <c r="B211" t="n">
-        <v>2.70544393640237</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C211" t="n">
-        <v>0.228794706405753</v>
+        <v>1.27953299407242</v>
       </c>
       <c r="D211" t="n">
-        <v>0.140505592505816</v>
+        <v>0.782563010073352</v>
       </c>
       <c r="E211" t="n">
-        <v>7.68121555183716</v>
+        <v>8.19964863872559</v>
       </c>
       <c r="F211" t="n">
-        <v>11.1907578587617</v>
+        <v>13.4068705497172</v>
       </c>
       <c r="G211" t="s">
         <v>68</v>
@@ -9225,7 +9225,7 @@
         <v>14</v>
       </c>
       <c r="K211" t="n">
-        <v>1.351</v>
+        <v>1.616</v>
       </c>
       <c r="L211" t="s">
         <v>15</v>
@@ -9239,19 +9239,19 @@
         <v>44378</v>
       </c>
       <c r="B212" t="n">
-        <v>2.65977661297179</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C212" t="n">
-        <v>0.226209576333729</v>
+        <v>1.27554841074043</v>
       </c>
       <c r="D212" t="n">
-        <v>0.139307806361607</v>
+        <v>0.77883905480113</v>
       </c>
       <c r="E212" t="n">
-        <v>7.61815450333546</v>
+        <v>8.22526286317913</v>
       </c>
       <c r="F212" t="n">
-        <v>11.1132576189053</v>
+        <v>13.4709744052696</v>
       </c>
       <c r="G212" t="s">
         <v>68</v>
@@ -9266,7 +9266,7 @@
         <v>14</v>
       </c>
       <c r="K212" t="n">
-        <v>2.643</v>
+        <v>3.217</v>
       </c>
       <c r="L212" t="s">
         <v>15</v>
@@ -9280,19 +9280,19 @@
         <v>44409</v>
       </c>
       <c r="B213" t="n">
-        <v>2.61409177226432</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C213" t="n">
-        <v>0.223672521400011</v>
+        <v>1.27158946503466</v>
       </c>
       <c r="D213" t="n">
-        <v>0.138125046937084</v>
+        <v>0.77514515398221</v>
       </c>
       <c r="E213" t="n">
-        <v>7.55536772023775</v>
+        <v>8.25087126116166</v>
       </c>
       <c r="F213" t="n">
-        <v>11.03609177306</v>
+        <v>13.535169405563</v>
       </c>
       <c r="G213" t="s">
         <v>68</v>
@@ -9307,7 +9307,7 @@
         <v>69</v>
       </c>
       <c r="K213" t="n">
-        <v>0.654</v>
+        <v>0.81</v>
       </c>
       <c r="L213" t="s">
         <v>15</v>
@@ -9321,19 +9321,19 @@
         <v>44440</v>
       </c>
       <c r="B214" t="n">
-        <v>2.56837435253578</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C214" t="n">
-        <v>0.221182137417511</v>
+        <v>1.26765586403197</v>
       </c>
       <c r="D214" t="n">
-        <v>0.136957028005834</v>
+        <v>0.771480925777955</v>
       </c>
       <c r="E214" t="n">
-        <v>7.49285452786144</v>
+        <v>8.27647413682125</v>
       </c>
       <c r="F214" t="n">
-        <v>10.9592600667608</v>
+        <v>13.5994560882638</v>
       </c>
       <c r="G214" t="s">
         <v>68</v>
@@ -9348,7 +9348,7 @@
         <v>69</v>
       </c>
       <c r="K214" t="n">
-        <v>0.429</v>
+        <v>0.541</v>
       </c>
       <c r="L214" t="s">
         <v>15</v>
@@ -9362,19 +9362,19 @@
         <v>44470</v>
       </c>
       <c r="B215" t="n">
-        <v>2.52260784536144</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C215" t="n">
-        <v>0.218737078042653</v>
+        <v>1.26374731987251</v>
       </c>
       <c r="D215" t="n">
-        <v>0.135803470775816</v>
+        <v>0.767845995297327</v>
       </c>
       <c r="E215" t="n">
-        <v>7.43061423958175</v>
+        <v>8.30207178924731</v>
       </c>
       <c r="F215" t="n">
-        <v>10.8827622311744</v>
+        <v>13.6638349842377</v>
       </c>
       <c r="G215" t="s">
         <v>68</v>
@@ -9389,7 +9389,7 @@
         <v>14</v>
       </c>
       <c r="K215" t="n">
-        <v>1.26</v>
+        <v>1.616</v>
       </c>
       <c r="L215" t="s">
         <v>15</v>
@@ -9403,19 +9403,19 @@
         <v>44501</v>
       </c>
       <c r="B216" t="n">
-        <v>2.47677408930698</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C216" t="n">
-        <v>0.216336051663842</v>
+        <v>1.25986354964106</v>
       </c>
       <c r="D216" t="n">
-        <v>0.134664103643799</v>
+        <v>0.764239994429522</v>
       </c>
       <c r="E216" t="n">
-        <v>7.36864615673342</v>
+        <v>8.32766451258915</v>
       </c>
       <c r="F216" t="n">
-        <v>10.8065979831866</v>
+        <v>13.7283066177165</v>
       </c>
       <c r="G216" t="s">
         <v>68</v>
@@ -9424,13 +9424,13 @@
         <v>1</v>
       </c>
       <c r="I216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J216" t="s">
         <v>14</v>
       </c>
       <c r="K216" t="n">
-        <v>2.462</v>
+        <v>3.217</v>
       </c>
       <c r="L216" t="s">
         <v>15</v>
@@ -9444,19 +9444,19 @@
         <v>44531</v>
       </c>
       <c r="B217" t="n">
-        <v>2.43085302467042</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C217" t="n">
-        <v>0.213977818497155</v>
+        <v>1.25600427525195</v>
       </c>
       <c r="D217" t="n">
-        <v>0.133538661959741</v>
+        <v>0.76066256168165</v>
       </c>
       <c r="E217" t="n">
-        <v>7.3069495685059</v>
+        <v>8.35325259617117</v>
       </c>
       <c r="F217" t="n">
-        <v>10.7307670254878</v>
+        <v>13.792871506461</v>
       </c>
       <c r="G217" t="s">
         <v>68</v>
@@ -9465,13 +9465,13 @@
         <v>3</v>
       </c>
       <c r="I217" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J217" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="K217" t="n">
-        <v>0.811</v>
+        <v>1.079</v>
       </c>
       <c r="L217" t="s">
         <v>15</v>
@@ -9485,19 +9485,19 @@
         <v>44562</v>
       </c>
       <c r="B218" t="n">
-        <v>2.38482239997813</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C218" t="n">
-        <v>0.211661187872842</v>
+        <v>1.2521692233373</v>
       </c>
       <c r="D218" t="n">
-        <v>0.132426887800641</v>
+        <v>0.757113342021273</v>
       </c>
       <c r="E218" t="n">
-        <v>7.24552375183173</v>
+        <v>8.37883632460457</v>
       </c>
       <c r="F218" t="n">
-        <v>10.6552690466572</v>
+        <v>13.8575301619181</v>
       </c>
       <c r="G218" t="s">
         <v>68</v>
@@ -9506,13 +9506,13 @@
         <v>1</v>
       </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J218" t="s">
         <v>14</v>
       </c>
       <c r="K218" t="n">
-        <v>2.371</v>
+        <v>3.217</v>
       </c>
       <c r="L218" t="s">
         <v>15</v>
@@ -9526,19 +9526,19 @@
         <v>44593</v>
       </c>
       <c r="B219" t="n">
-        <v>2.33865741817148</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C219" t="n">
-        <v>0.20938501569769</v>
+        <v>1.24835812513854</v>
       </c>
       <c r="D219" t="n">
-        <v>0.131328529753418</v>
+        <v>0.753591986723628</v>
       </c>
       <c r="E219" t="n">
-        <v>7.1843679712678</v>
+        <v>8.4044159778958</v>
       </c>
       <c r="F219" t="n">
-        <v>10.5801037212467</v>
+        <v>13.9222830893744</v>
       </c>
       <c r="G219" t="s">
         <v>68</v>
@@ -9547,13 +9547,13 @@
         <v>1</v>
       </c>
       <c r="I219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J219" t="s">
         <v>14</v>
       </c>
       <c r="K219" t="n">
-        <v>2.325</v>
+        <v>3.217</v>
       </c>
       <c r="L219" t="s">
         <v>15</v>
@@ -9567,19 +9567,19 @@
         <v>44621</v>
       </c>
       <c r="B220" t="n">
-        <v>2.29233030669711</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C220" t="n">
-        <v>0.207148202079675</v>
+        <v>1.24457071640115</v>
       </c>
       <c r="D220" t="n">
-        <v>0.130243342706371</v>
+        <v>0.750098153223377</v>
       </c>
       <c r="E220" t="n">
-        <v>7.12348147886924</v>
+        <v>8.42999183155192</v>
       </c>
       <c r="F220" t="n">
-        <v>10.5052707098626</v>
+        <v>13.9871307881037</v>
       </c>
       <c r="G220" t="s">
         <v>68</v>
@@ -9588,13 +9588,13 @@
         <v>1</v>
       </c>
       <c r="I220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J220" t="s">
         <v>14</v>
       </c>
       <c r="K220" t="n">
-        <v>2.28</v>
+        <v>3.217</v>
       </c>
       <c r="L220" t="s">
         <v>15</v>
@@ -9608,19 +9608,19 @@
         <v>44652</v>
       </c>
       <c r="B221" t="n">
-        <v>2.24580979060038</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C221" t="n">
-        <v>0.204949689102547</v>
+        <v>1.24080673727232</v>
       </c>
       <c r="D221" t="n">
-        <v>0.129171087648834</v>
+        <v>0.746631504970702</v>
       </c>
       <c r="E221" t="n">
-        <v>7.06286351405554</v>
+        <v>8.45556415668283</v>
       </c>
       <c r="F221" t="n">
-        <v>10.4307696592469</v>
+        <v>14.0520737515116</v>
       </c>
       <c r="G221" t="s">
         <v>68</v>
@@ -9629,13 +9629,13 @@
         <v>2</v>
       </c>
       <c r="I221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J221" t="s">
         <v>14</v>
       </c>
       <c r="K221" t="n">
-        <v>1.122</v>
+        <v>1.616</v>
       </c>
       <c r="L221" t="s">
         <v>15</v>
@@ -9649,19 +9649,19 @@
         <v>44682</v>
       </c>
       <c r="B222" t="n">
-        <v>2.19906044060042</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C222" t="n">
-        <v>0.202788458739065</v>
+        <v>1.23706593220168</v>
       </c>
       <c r="D222" t="n">
-        <v>0.128111531478642</v>
+        <v>0.743191711291613</v>
       </c>
       <c r="E222" t="n">
-        <v>7.00251330346862</v>
+        <v>8.48113322010061</v>
       </c>
       <c r="F222" t="n">
-        <v>10.3566002023572</v>
+        <v>14.1171124672752</v>
       </c>
       <c r="G222" t="s">
         <v>68</v>
@@ -9670,13 +9670,13 @@
         <v>5</v>
       </c>
       <c r="I222" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="J222" t="s">
         <v>69</v>
       </c>
       <c r="K222" t="n">
-        <v>0.441</v>
+        <v>0.649</v>
       </c>
       <c r="L222" t="s">
         <v>15</v>
@@ -9690,19 +9690,19 @@
         <v>44713</v>
       </c>
       <c r="B223" t="n">
-        <v>2.15204185805369</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C223" t="n">
-        <v>0.200663530892597</v>
+        <v>1.23334804984477</v>
       </c>
       <c r="D223" t="n">
-        <v>0.127064446817031</v>
+        <v>0.739778447252311</v>
       </c>
       <c r="E223" t="n">
-        <v>6.94243006082248</v>
+        <v>8.50669928441603</v>
       </c>
       <c r="F223" t="n">
-        <v>10.2827619584451</v>
+        <v>14.1822474174786</v>
       </c>
       <c r="G223" t="s">
         <v>68</v>
@@ -9711,13 +9711,13 @@
         <v>5</v>
       </c>
       <c r="I223" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="J223" t="s">
         <v>69</v>
       </c>
       <c r="K223" t="n">
-        <v>0.432</v>
+        <v>0.649</v>
       </c>
       <c r="L223" t="s">
         <v>15</v>
@@ -9731,19 +9731,19 @@
         <v>44743</v>
       </c>
       <c r="B224" t="n">
-        <v>2.10470764422702</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C224" t="n">
-        <v>0.198573961557679</v>
+        <v>1.22965284296929</v>
       </c>
       <c r="D224" t="n">
-        <v>0.126029611830657</v>
+        <v>0.736391393527461</v>
       </c>
       <c r="E224" t="n">
-        <v>6.8826129867439</v>
+        <v>8.53226260813231</v>
       </c>
       <c r="F224" t="n">
-        <v>10.2092545331345</v>
+        <v>14.2474790787451</v>
       </c>
       <c r="G224" t="s">
         <v>68</v>
@@ -9752,13 +9752,13 @@
         <v>4</v>
       </c>
       <c r="I224" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J224" t="s">
         <v>69</v>
       </c>
       <c r="K224" t="n">
-        <v>0.527</v>
+        <v>0.81</v>
       </c>
       <c r="L224" t="s">
         <v>15</v>
@@ -9772,19 +9772,19 @@
         <v>44774</v>
       </c>
       <c r="B225" t="n">
-        <v>2.05700408007253</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C225" t="n">
-        <v>0.196518841090921</v>
+        <v>1.22598006836396</v>
       </c>
       <c r="D225" t="n">
-        <v>0.125006810060385</v>
+        <v>0.73303023627225</v>
       </c>
       <c r="E225" t="n">
-        <v>6.823061268604</v>
+        <v>8.55782344573623</v>
       </c>
       <c r="F225" t="n">
-        <v>10.1360775184971</v>
+        <v>14.3128079223648</v>
       </c>
       <c r="G225" t="s">
         <v>68</v>
@@ -9793,13 +9793,13 @@
         <v>3</v>
       </c>
       <c r="I225" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J225" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="K225" t="n">
-        <v>0.687</v>
+        <v>1.079</v>
       </c>
       <c r="L225" t="s">
         <v>15</v>
@@ -9813,19 +9813,19 @@
         <v>44805</v>
       </c>
       <c r="B226" t="n">
-        <v>2.008868410937</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C226" t="n">
-        <v>0.194497292584381</v>
+        <v>1.22232948675002</v>
       </c>
       <c r="D226" t="n">
-        <v>0.123995830256554</v>
+        <v>0.729694666998091</v>
       </c>
       <c r="E226" t="n">
-        <v>6.76377408034013</v>
+        <v>8.5833820477867</v>
       </c>
       <c r="F226" t="n">
-        <v>10.0632304931282</v>
+        <v>14.3782344144196</v>
       </c>
       <c r="G226" t="s">
         <v>68</v>
@@ -9834,13 +9834,13 @@
         <v>0</v>
       </c>
       <c r="I226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J226" t="s">
         <v>14</v>
       </c>
       <c r="K226" t="n">
-        <v>201.887</v>
+        <v>324.909</v>
       </c>
       <c r="L226" t="s">
         <v>41</v>
@@ -9854,19 +9854,19 @@
         <v>44835</v>
       </c>
       <c r="B227" t="n">
-        <v>1.96022658200925</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C227" t="n">
-        <v>0.192508470334165</v>
+        <v>1.21870086269504</v>
       </c>
       <c r="D227" t="n">
-        <v>0.122996466220426</v>
+        <v>0.726384382451847</v>
       </c>
       <c r="E227" t="n">
-        <v>6.70475058226746</v>
+        <v>8.60893866100088</v>
       </c>
       <c r="F227" t="n">
-        <v>9.99071302222049</v>
+        <v>14.4437590159036</v>
       </c>
       <c r="G227" t="s">
         <v>68</v>
@@ -9875,13 +9875,13 @@
         <v>2</v>
       </c>
       <c r="I227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J227" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="K227" t="n">
-        <v>0.98</v>
+        <v>1.616</v>
       </c>
       <c r="L227" t="s">
         <v>15</v>
@@ -9895,19 +9895,19 @@
         <v>44866</v>
       </c>
       <c r="B228" t="n">
-        <v>1.91099019388835</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C228" t="n">
-        <v>0.190551558397616</v>
+        <v>1.21509396452928</v>
       </c>
       <c r="D228" t="n">
-        <v>0.122008516651548</v>
+        <v>0.72309908449847</v>
       </c>
       <c r="E228" t="n">
-        <v>6.64598992088011</v>
+        <v>8.63449352833784</v>
       </c>
       <c r="F228" t="n">
-        <v>9.91852465763689</v>
+        <v>14.5093821828406</v>
       </c>
       <c r="G228" t="s">
         <v>68</v>
@@ -9916,13 +9916,13 @@
         <v>2</v>
       </c>
       <c r="I228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J228" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="K228" t="n">
-        <v>0.956</v>
+        <v>1.616</v>
       </c>
       <c r="L228" t="s">
         <v>15</v>
@@ -9936,19 +9936,19 @@
         <v>44896</v>
       </c>
       <c r="B229" t="n">
-        <v>1.86105232396187</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C229" t="n">
-        <v>0.188625769232996</v>
+        <v>1.21150856426425</v>
       </c>
       <c r="D229" t="n">
-        <v>0.121031785000751</v>
+        <v>0.719838480006911</v>
       </c>
       <c r="E229" t="n">
-        <v>6.587491228641</v>
+        <v>8.66004688908005</v>
       </c>
       <c r="F229" t="n">
-        <v>9.84666493798207</v>
+        <v>14.5751043663986</v>
       </c>
       <c r="G229" t="s">
         <v>68</v>
@@ -9957,13 +9957,13 @@
         <v>3</v>
       </c>
       <c r="I229" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J229" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="K229" t="n">
-        <v>0.622</v>
+        <v>1.079</v>
       </c>
       <c r="L229" t="s">
         <v>15</v>
@@ -9977,19 +9977,19 @@
         <v>44927</v>
       </c>
       <c r="B230" t="n">
-        <v>1.81028165220069</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C230" t="n">
-        <v>0.186730342416022</v>
+        <v>1.20794443751352</v>
       </c>
       <c r="D230" t="n">
-        <v>0.120066079328556</v>
+        <v>0.716602280739228</v>
       </c>
       <c r="E230" t="n">
-        <v>6.52925362376003</v>
+        <v>8.68559897891249</v>
       </c>
       <c r="F230" t="n">
-        <v>9.7751333886729</v>
+        <v>14.6409260130005</v>
       </c>
       <c r="G230" t="s">
         <v>68</v>
@@ -9998,13 +9998,13 @@
         <v>3</v>
       </c>
       <c r="I230" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J230" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="K230" t="n">
-        <v>0.605</v>
+        <v>1.079</v>
       </c>
       <c r="L230" t="s">
         <v>15</v>
@@ -10018,19 +10018,19 @@
         <v>44958</v>
       </c>
       <c r="B231" t="n">
-        <v>1.7585139694917</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C231" t="n">
-        <v>0.184864543428103</v>
+        <v>1.2044013634157</v>
       </c>
       <c r="D231" t="n">
-        <v>0.119111212168738</v>
+        <v>0.713390203242748</v>
       </c>
       <c r="E231" t="n">
-        <v>6.47127620995994</v>
+        <v>8.71115002999974</v>
       </c>
       <c r="F231" t="n">
-        <v>9.70392952200745</v>
+        <v>14.7068475644322</v>
       </c>
       <c r="G231" t="s">
         <v>68</v>
@@ -10039,13 +10039,13 @@
         <v>3</v>
       </c>
       <c r="I231" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J231" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="K231" t="n">
-        <v>0.588</v>
+        <v>1.079</v>
       </c>
       <c r="L231" t="s">
         <v>15</v>
@@ -10059,19 +10059,19 @@
         <v>44986</v>
       </c>
       <c r="B232" t="n">
-        <v>1.70553948977734</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C232" t="n">
-        <v>0.183027662511495</v>
+        <v>1.20087912455951</v>
       </c>
       <c r="D232" t="n">
-        <v>0.118167000396836</v>
+        <v>0.710201968745206</v>
       </c>
       <c r="E232" t="n">
-        <v>6.41355807622922</v>
+        <v>8.7367002710609</v>
       </c>
       <c r="F232" t="n">
-        <v>9.6330528372329</v>
+        <v>14.7728694579478</v>
       </c>
       <c r="G232" t="s">
         <v>68</v>
@@ -10080,13 +10080,13 @@
         <v>6</v>
       </c>
       <c r="I232" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="J232" t="s">
         <v>69</v>
       </c>
       <c r="K232" t="n">
-        <v>0.285</v>
+        <v>0.541</v>
       </c>
       <c r="L232" t="s">
         <v>15</v>
@@ -10100,19 +10100,19 @@
         <v>45017</v>
       </c>
       <c r="B233" t="n">
-        <v>1.65108312366445</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C233" t="n">
-        <v>0.181219013586981</v>
+        <v>1.1973775069108</v>
       </c>
       <c r="D233" t="n">
-        <v>0.117233265103382</v>
+        <v>0.70703730305276</v>
       </c>
       <c r="E233" t="n">
-        <v>6.3560982965615</v>
+        <v>8.76224992744251</v>
       </c>
       <c r="F233" t="n">
-        <v>9.56250282061209</v>
+        <v>14.8389921263709</v>
       </c>
       <c r="G233" t="s">
         <v>68</v>
@@ -10121,13 +10121,13 @@
         <v>4</v>
       </c>
       <c r="I233" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J233" t="s">
         <v>69</v>
       </c>
       <c r="K233" t="n">
-        <v>0.414</v>
+        <v>0.81</v>
       </c>
       <c r="L233" t="s">
         <v>15</v>
@@ -10141,19 +10141,19 @@
         <v>45047</v>
       </c>
       <c r="B234" t="n">
-        <v>1.59477227537923</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C234" t="n">
-        <v>0.179437933229999</v>
+        <v>1.19389629974161</v>
       </c>
       <c r="D234" t="n">
-        <v>0.116309831471665</v>
+        <v>0.703895936450768</v>
       </c>
       <c r="E234" t="n">
-        <v>6.29889592968051</v>
+        <v>8.78779922118957</v>
       </c>
       <c r="F234" t="n">
-        <v>9.4922789454888</v>
+        <v>14.905215998195</v>
       </c>
       <c r="G234" t="s">
         <v>68</v>
@@ -10162,13 +10162,13 @@
         <v>2</v>
       </c>
       <c r="I234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J234" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="K234" t="n">
-        <v>0.798</v>
+        <v>1.616</v>
       </c>
       <c r="L234" t="s">
         <v>15</v>
@@ -10182,19 +10182,19 @@
         <v>45078</v>
       </c>
       <c r="B235" t="n">
-        <v>1.53608094081597</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C235" t="n">
-        <v>0.177683779701461</v>
+        <v>1.19043529556106</v>
       </c>
       <c r="D235" t="n">
-        <v>0.115396528659825</v>
+        <v>0.700777603607269</v>
       </c>
       <c r="E235" t="n">
-        <v>6.24195001875013</v>
+        <v>8.81334837111464</v>
       </c>
       <c r="F235" t="n">
-        <v>9.42238067235166</v>
+        <v>14.9715414976792</v>
       </c>
       <c r="G235" t="s">
         <v>68</v>
@@ -10203,13 +10203,13 @@
         <v>4</v>
       </c>
       <c r="I235" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J235" t="s">
         <v>69</v>
       </c>
       <c r="K235" t="n">
-        <v>0.386</v>
+        <v>0.81</v>
       </c>
       <c r="L235" t="s">
         <v>15</v>
@@ -10223,19 +10223,19 @@
         <v>45108</v>
       </c>
       <c r="B236" t="n">
-        <v>1.47422458555131</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C236" t="n">
-        <v>0.175955932029795</v>
+        <v>1.18699429004807</v>
       </c>
       <c r="D236" t="n">
-        <v>0.1144931896871</v>
+        <v>0.697682043479045</v>
       </c>
       <c r="E236" t="n">
-        <v>6.18525959106843</v>
+        <v>8.83889759286506</v>
       </c>
       <c r="F236" t="n">
-        <v>9.3528074488969</v>
+        <v>15.037969044943</v>
       </c>
       <c r="G236" t="s">
         <v>68</v>
@@ -10244,13 +10244,13 @@
         <v>6</v>
       </c>
       <c r="I236" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="J236" t="s">
         <v>69</v>
       </c>
       <c r="K236" t="n">
-        <v>0.247</v>
+        <v>0.541</v>
       </c>
       <c r="L236" t="s">
         <v>15</v>
@@ -10264,19 +10264,19 @@
         <v>45139</v>
       </c>
       <c r="B237" t="n">
-        <v>1.40793968747258</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C237" t="n">
-        <v>0.17425378914096</v>
+        <v>1.18357308198586</v>
       </c>
       <c r="D237" t="n">
-        <v>0.113599651324046</v>
+        <v>0.694608999220212</v>
       </c>
       <c r="E237" t="n">
-        <v>6.12882365774515</v>
+        <v>8.86444709898851</v>
       </c>
       <c r="F237" t="n">
-        <v>9.28355871008949</v>
+        <v>15.1044990560571</v>
       </c>
       <c r="G237" t="s">
         <v>68</v>
@@ -10285,13 +10285,13 @@
         <v>4</v>
       </c>
       <c r="I237" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="J237" t="s">
         <v>69</v>
       </c>
       <c r="K237" t="n">
-        <v>0.354</v>
+        <v>0.81</v>
       </c>
       <c r="L237" t="s">
         <v>15</v>
@@ -10305,19 +10305,19 @@
         <v>45170</v>
       </c>
       <c r="B238" t="n">
-        <v>1.33494152543683</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C238" t="n">
-        <v>0.172576769033477</v>
+        <v>1.18017147319816</v>
       </c>
       <c r="D238" t="n">
-        <v>0.112715753986582</v>
+        <v>0.691558218093233</v>
       </c>
       <c r="E238" t="n">
-        <v>6.07264121336141</v>
+        <v>8.88999709899679</v>
       </c>
       <c r="F238" t="n">
-        <v>9.21463387822312</v>
+        <v>15.1711319431331</v>
       </c>
       <c r="G238" t="s">
         <v>68</v>
@@ -10326,13 +10326,13 @@
         <v>3</v>
       </c>
       <c r="I238" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J238" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="K238" t="n">
-        <v>0.447</v>
+        <v>1.079</v>
       </c>
       <c r="L238" t="s">
         <v>15</v>
@@ -10346,19 +10346,19 @@
         <v>45200</v>
       </c>
       <c r="B239" t="n">
-        <v>1.25019049888966</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C239" t="n">
-        <v>0.170924307995682</v>
+        <v>1.17678926848708</v>
       </c>
       <c r="D239" t="n">
-        <v>0.111841341633679</v>
+        <v>0.688529451382296</v>
       </c>
       <c r="E239" t="n">
-        <v>6.01671123561096</v>
+        <v>8.91554779942795</v>
       </c>
       <c r="F239" t="n">
-        <v>9.14603236297871</v>
+        <v>15.2378681144099</v>
       </c>
       <c r="G239" t="s">
         <v>68</v>
@@ -10367,13 +10367,13 @@
         <v>7</v>
       </c>
       <c r="I239" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="J239" t="s">
         <v>69</v>
       </c>
       <c r="K239" t="n">
-        <v>0.18</v>
+        <v>0.463</v>
       </c>
       <c r="L239" t="s">
         <v>15</v>
@@ -10387,19 +10387,19 @@
         <v>45231</v>
       </c>
       <c r="B240" t="n">
-        <v>1.13603131890598</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C240" t="n">
-        <v>0.169295859862633</v>
+        <v>1.17342627557256</v>
       </c>
       <c r="D240" t="n">
-        <v>0.110976261668565</v>
+        <v>0.685522454308967</v>
       </c>
       <c r="E240" t="n">
-        <v>5.96103268492168</v>
+        <v>8.94109940390683</v>
       </c>
       <c r="F240" t="n">
-        <v>9.0777535614814</v>
+        <v>15.3047079743383</v>
       </c>
       <c r="G240" t="s">
         <v>68</v>
@@ -10408,13 +10408,13 @@
         <v>4</v>
       </c>
       <c r="I240" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="J240" t="s">
         <v>69</v>
       </c>
       <c r="K240" t="n">
-        <v>0.286</v>
+        <v>0.81</v>
       </c>
       <c r="L240" t="s">
         <v>15</v>
@@ -10428,19 +10428,19 @@
         <v>45261</v>
       </c>
       <c r="B241" t="n">
-        <v>0.876664834500467</v>
+        <v>3.23909261569509</v>
       </c>
       <c r="C241" t="n">
-        <v>0.16769089531028</v>
+        <v>1.17008230503341</v>
       </c>
       <c r="D241" t="n">
-        <v>0.110120364843284</v>
+        <v>0.682536985950052</v>
       </c>
       <c r="E241" t="n">
-        <v>5.90560450405645</v>
+        <v>8.96665211320403</v>
       </c>
       <c r="F241" t="n">
-        <v>9.00979685835627</v>
+        <v>15.3716519236632</v>
       </c>
       <c r="G241" t="s">
         <v>68</v>
@@ -10449,13 +10449,13 @@
         <v>1</v>
       </c>
       <c r="I241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J241" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="K241" t="n">
-        <v>0.878</v>
+        <v>3.217</v>
       </c>
       <c r="L241" t="s">
         <v>15</v>

--- a/Outcome/Appendix/figure_data/fig10.xlsx
+++ b/Outcome/Appendix/figure_data/fig10.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -217,15 +217,6 @@
   <si>
     <t xml:space="preserve">Rubella</t>
   </si>
-  <si>
-    <t xml:space="preserve">Other tetanus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Increase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pertussis</t>
-  </si>
 </sst>
 </file>
 
@@ -280,8 +271,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M289" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M289"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M193" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M193"/>
   <tableColumns count="13">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="mean"/>
@@ -8496,3942 +8487,6 @@
         <v>64</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="B194" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C194" t="n">
-        <v>1.35150455359448</v>
-      </c>
-      <c r="D194" t="n">
-        <v>0.8508760771789</v>
-      </c>
-      <c r="E194" t="n">
-        <v>7.76299343213201</v>
-      </c>
-      <c r="F194" t="n">
-        <v>12.3304923648059</v>
-      </c>
-      <c r="G194" t="s">
-        <v>68</v>
-      </c>
-      <c r="H194" t="n">
-        <v>0</v>
-      </c>
-      <c r="I194" t="n">
-        <v>3</v>
-      </c>
-      <c r="J194" t="s">
-        <v>14</v>
-      </c>
-      <c r="K194" t="n">
-        <v>324.909</v>
-      </c>
-      <c r="L194" t="s">
-        <v>41</v>
-      </c>
-      <c r="M194" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="1" t="n">
-        <v>43862</v>
-      </c>
-      <c r="B195" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C195" t="n">
-        <v>1.34703374978168</v>
-      </c>
-      <c r="D195" t="n">
-        <v>0.846575113307784</v>
-      </c>
-      <c r="E195" t="n">
-        <v>7.78875880040192</v>
-      </c>
-      <c r="F195" t="n">
-        <v>12.3931365429071</v>
-      </c>
-      <c r="G195" t="s">
-        <v>68</v>
-      </c>
-      <c r="H195" t="n">
-        <v>2</v>
-      </c>
-      <c r="I195" t="n">
-        <v>1</v>
-      </c>
-      <c r="J195" t="s">
-        <v>14</v>
-      </c>
-      <c r="K195" t="n">
-        <v>1.616</v>
-      </c>
-      <c r="L195" t="s">
-        <v>15</v>
-      </c>
-      <c r="M195" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="1" t="n">
-        <v>43891</v>
-      </c>
-      <c r="B196" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C196" t="n">
-        <v>1.34259447299923</v>
-      </c>
-      <c r="D196" t="n">
-        <v>0.842311949144005</v>
-      </c>
-      <c r="E196" t="n">
-        <v>7.81451226267372</v>
-      </c>
-      <c r="F196" t="n">
-        <v>12.4558614937288</v>
-      </c>
-      <c r="G196" t="s">
-        <v>68</v>
-      </c>
-      <c r="H196" t="n">
-        <v>1</v>
-      </c>
-      <c r="I196" t="n">
-        <v>2</v>
-      </c>
-      <c r="J196" t="s">
-        <v>14</v>
-      </c>
-      <c r="K196" t="n">
-        <v>3.217</v>
-      </c>
-      <c r="L196" t="s">
-        <v>15</v>
-      </c>
-      <c r="M196" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="1" t="n">
-        <v>43922</v>
-      </c>
-      <c r="B197" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C197" t="n">
-        <v>1.33818632194869</v>
-      </c>
-      <c r="D197" t="n">
-        <v>0.838086053169818</v>
-      </c>
-      <c r="E197" t="n">
-        <v>7.84025423139295</v>
-      </c>
-      <c r="F197" t="n">
-        <v>12.5186679021427</v>
-      </c>
-      <c r="G197" t="s">
-        <v>68</v>
-      </c>
-      <c r="H197" t="n">
-        <v>5</v>
-      </c>
-      <c r="I197" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J197" t="s">
-        <v>69</v>
-      </c>
-      <c r="K197" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="L197" t="s">
-        <v>15</v>
-      </c>
-      <c r="M197" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="1" t="n">
-        <v>43952</v>
-      </c>
-      <c r="B198" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C198" t="n">
-        <v>1.33380890310377</v>
-      </c>
-      <c r="D198" t="n">
-        <v>0.833896904655806</v>
-      </c>
-      <c r="E198" t="n">
-        <v>7.86598511123763</v>
-      </c>
-      <c r="F198" t="n">
-        <v>12.5815564423769</v>
-      </c>
-      <c r="G198" t="s">
-        <v>68</v>
-      </c>
-      <c r="H198" t="n">
-        <v>4</v>
-      </c>
-      <c r="I198" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J198" t="s">
-        <v>69</v>
-      </c>
-      <c r="K198" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="L198" t="s">
-        <v>15</v>
-      </c>
-      <c r="M198" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="1" t="n">
-        <v>43983</v>
-      </c>
-      <c r="B199" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C199" t="n">
-        <v>1.3294618305059</v>
-      </c>
-      <c r="D199" t="n">
-        <v>0.82974399337001</v>
-      </c>
-      <c r="E199" t="n">
-        <v>7.89170529932253</v>
-      </c>
-      <c r="F199" t="n">
-        <v>12.644527778307</v>
-      </c>
-      <c r="G199" t="s">
-        <v>68</v>
-      </c>
-      <c r="H199" t="n">
-        <v>1</v>
-      </c>
-      <c r="I199" t="n">
-        <v>2</v>
-      </c>
-      <c r="J199" t="s">
-        <v>14</v>
-      </c>
-      <c r="K199" t="n">
-        <v>3.217</v>
-      </c>
-      <c r="L199" t="s">
-        <v>15</v>
-      </c>
-      <c r="M199" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="1" t="n">
-        <v>44013</v>
-      </c>
-      <c r="B200" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C200" t="n">
-        <v>1.32514472556671</v>
-      </c>
-      <c r="D200" t="n">
-        <v>0.825626819296882</v>
-      </c>
-      <c r="E200" t="n">
-        <v>7.91741518539687</v>
-      </c>
-      <c r="F200" t="n">
-        <v>12.7075825637367</v>
-      </c>
-      <c r="G200" t="s">
-        <v>68</v>
-      </c>
-      <c r="H200" t="n">
-        <v>6</v>
-      </c>
-      <c r="I200" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J200" t="s">
-        <v>69</v>
-      </c>
-      <c r="K200" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="L200" t="s">
-        <v>15</v>
-      </c>
-      <c r="M200" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="1" t="n">
-        <v>44044</v>
-      </c>
-      <c r="B201" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C201" t="n">
-        <v>1.32085721687695</v>
-      </c>
-      <c r="D201" t="n">
-        <v>0.82154489236567</v>
-      </c>
-      <c r="E201" t="n">
-        <v>7.94311515203528</v>
-      </c>
-      <c r="F201" t="n">
-        <v>12.7707214426702</v>
-      </c>
-      <c r="G201" t="s">
-        <v>68</v>
-      </c>
-      <c r="H201" t="n">
-        <v>3</v>
-      </c>
-      <c r="I201" t="n">
-        <v>0</v>
-      </c>
-      <c r="J201" t="s">
-        <v>14</v>
-      </c>
-      <c r="K201" t="n">
-        <v>1.079</v>
-      </c>
-      <c r="L201" t="s">
-        <v>15</v>
-      </c>
-      <c r="M201" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="1" t="n">
-        <v>44075</v>
-      </c>
-      <c r="B202" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C202" t="n">
-        <v>1.31659894002169</v>
-      </c>
-      <c r="D202" t="n">
-        <v>0.817497732187837</v>
-      </c>
-      <c r="E202" t="n">
-        <v>7.96880557482266</v>
-      </c>
-      <c r="F202" t="n">
-        <v>12.8339450495744</v>
-      </c>
-      <c r="G202" t="s">
-        <v>68</v>
-      </c>
-      <c r="H202" t="n">
-        <v>7</v>
-      </c>
-      <c r="I202" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J202" t="s">
-        <v>69</v>
-      </c>
-      <c r="K202" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="L202" t="s">
-        <v>15</v>
-      </c>
-      <c r="M202" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="1" t="n">
-        <v>44105</v>
-      </c>
-      <c r="B203" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C203" t="n">
-        <v>1.31236953740157</v>
-      </c>
-      <c r="D203" t="n">
-        <v>0.813484867803166</v>
-      </c>
-      <c r="E203" t="n">
-        <v>7.99448682253289</v>
-      </c>
-      <c r="F203" t="n">
-        <v>12.8972540096333</v>
-      </c>
-      <c r="G203" t="s">
-        <v>68</v>
-      </c>
-      <c r="H203" t="n">
-        <v>3</v>
-      </c>
-      <c r="I203" t="n">
-        <v>0</v>
-      </c>
-      <c r="J203" t="s">
-        <v>14</v>
-      </c>
-      <c r="K203" t="n">
-        <v>1.079</v>
-      </c>
-      <c r="L203" t="s">
-        <v>15</v>
-      </c>
-      <c r="M203" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="1" t="n">
-        <v>44136</v>
-      </c>
-      <c r="B204" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C204" t="n">
-        <v>1.30816865805979</v>
-      </c>
-      <c r="D204" t="n">
-        <v>0.809505837434201</v>
-      </c>
-      <c r="E204" t="n">
-        <v>8.02015925730189</v>
-      </c>
-      <c r="F204" t="n">
-        <v>12.9606489389933</v>
-      </c>
-      <c r="G204" t="s">
-        <v>68</v>
-      </c>
-      <c r="H204" t="n">
-        <v>0</v>
-      </c>
-      <c r="I204" t="n">
-        <v>3</v>
-      </c>
-      <c r="J204" t="s">
-        <v>14</v>
-      </c>
-      <c r="K204" t="n">
-        <v>324.909</v>
-      </c>
-      <c r="L204" t="s">
-        <v>41</v>
-      </c>
-      <c r="M204" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="1" t="n">
-        <v>44166</v>
-      </c>
-      <c r="B205" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C205" t="n">
-        <v>1.30399595751468</v>
-      </c>
-      <c r="D205" t="n">
-        <v>0.805560188248694</v>
-      </c>
-      <c r="E205" t="n">
-        <v>8.04582323479502</v>
-      </c>
-      <c r="F205" t="n">
-        <v>13.0241304450008</v>
-      </c>
-      <c r="G205" t="s">
-        <v>68</v>
-      </c>
-      <c r="H205" t="n">
-        <v>1</v>
-      </c>
-      <c r="I205" t="n">
-        <v>2</v>
-      </c>
-      <c r="J205" t="s">
-        <v>14</v>
-      </c>
-      <c r="K205" t="n">
-        <v>3.217</v>
-      </c>
-      <c r="L205" t="s">
-        <v>15</v>
-      </c>
-      <c r="M205" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="1" t="n">
-        <v>44197</v>
-      </c>
-      <c r="B206" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C206" t="n">
-        <v>1.29985109759761</v>
-      </c>
-      <c r="D206" t="n">
-        <v>0.801647476129748</v>
-      </c>
-      <c r="E206" t="n">
-        <v>8.07147910436919</v>
-      </c>
-      <c r="F206" t="n">
-        <v>13.0876991264329</v>
-      </c>
-      <c r="G206" t="s">
-        <v>68</v>
-      </c>
-      <c r="H206" t="n">
-        <v>3</v>
-      </c>
-      <c r="I206" t="n">
-        <v>0</v>
-      </c>
-      <c r="J206" t="s">
-        <v>14</v>
-      </c>
-      <c r="K206" t="n">
-        <v>1.079</v>
-      </c>
-      <c r="L206" t="s">
-        <v>15</v>
-      </c>
-      <c r="M206" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="1" t="n">
-        <v>44228</v>
-      </c>
-      <c r="B207" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C207" t="n">
-        <v>1.29573374629598</v>
-      </c>
-      <c r="D207" t="n">
-        <v>0.79776726545335</v>
-      </c>
-      <c r="E207" t="n">
-        <v>8.0971272092298</v>
-      </c>
-      <c r="F207" t="n">
-        <v>13.1513555737189</v>
-      </c>
-      <c r="G207" t="s">
-        <v>68</v>
-      </c>
-      <c r="H207" t="n">
-        <v>2</v>
-      </c>
-      <c r="I207" t="n">
-        <v>1</v>
-      </c>
-      <c r="J207" t="s">
-        <v>14</v>
-      </c>
-      <c r="K207" t="n">
-        <v>1.616</v>
-      </c>
-      <c r="L207" t="s">
-        <v>15</v>
-      </c>
-      <c r="M207" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="1" t="n">
-        <v>44256</v>
-      </c>
-      <c r="B208" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C208" t="n">
-        <v>1.29164357760125</v>
-      </c>
-      <c r="D208" t="n">
-        <v>0.793919128873017</v>
-      </c>
-      <c r="E208" t="n">
-        <v>8.12276788658285</v>
-      </c>
-      <c r="F208" t="n">
-        <v>13.2151003691568</v>
-      </c>
-      <c r="G208" t="s">
-        <v>68</v>
-      </c>
-      <c r="H208" t="n">
-        <v>2</v>
-      </c>
-      <c r="I208" t="n">
-        <v>1</v>
-      </c>
-      <c r="J208" t="s">
-        <v>14</v>
-      </c>
-      <c r="K208" t="n">
-        <v>1.616</v>
-      </c>
-      <c r="L208" t="s">
-        <v>15</v>
-      </c>
-      <c r="M208" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="1" t="n">
-        <v>44287</v>
-      </c>
-      <c r="B209" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C209" t="n">
-        <v>1.28758027136163</v>
-      </c>
-      <c r="D209" t="n">
-        <v>0.790102647111275</v>
-      </c>
-      <c r="E209" t="n">
-        <v>8.14840146778213</v>
-      </c>
-      <c r="F209" t="n">
-        <v>13.278934087121</v>
-      </c>
-      <c r="G209" t="s">
-        <v>68</v>
-      </c>
-      <c r="H209" t="n">
-        <v>0</v>
-      </c>
-      <c r="I209" t="n">
-        <v>3</v>
-      </c>
-      <c r="J209" t="s">
-        <v>14</v>
-      </c>
-      <c r="K209" t="n">
-        <v>324.909</v>
-      </c>
-      <c r="L209" t="s">
-        <v>41</v>
-      </c>
-      <c r="M209" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="1" t="n">
-        <v>44317</v>
-      </c>
-      <c r="B210" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C210" t="n">
-        <v>1.28354351313936</v>
-      </c>
-      <c r="D210" t="n">
-        <v>0.786317408757711</v>
-      </c>
-      <c r="E210" t="n">
-        <v>8.17402827847197</v>
-      </c>
-      <c r="F210" t="n">
-        <v>13.3428572942651</v>
-      </c>
-      <c r="G210" t="s">
-        <v>68</v>
-      </c>
-      <c r="H210" t="n">
-        <v>2</v>
-      </c>
-      <c r="I210" t="n">
-        <v>1</v>
-      </c>
-      <c r="J210" t="s">
-        <v>14</v>
-      </c>
-      <c r="K210" t="n">
-        <v>1.616</v>
-      </c>
-      <c r="L210" t="s">
-        <v>15</v>
-      </c>
-      <c r="M210" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="1" t="n">
-        <v>44348</v>
-      </c>
-      <c r="B211" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C211" t="n">
-        <v>1.27953299407242</v>
-      </c>
-      <c r="D211" t="n">
-        <v>0.782563010073352</v>
-      </c>
-      <c r="E211" t="n">
-        <v>8.19964863872559</v>
-      </c>
-      <c r="F211" t="n">
-        <v>13.4068705497172</v>
-      </c>
-      <c r="G211" t="s">
-        <v>68</v>
-      </c>
-      <c r="H211" t="n">
-        <v>2</v>
-      </c>
-      <c r="I211" t="n">
-        <v>1</v>
-      </c>
-      <c r="J211" t="s">
-        <v>14</v>
-      </c>
-      <c r="K211" t="n">
-        <v>1.616</v>
-      </c>
-      <c r="L211" t="s">
-        <v>15</v>
-      </c>
-      <c r="M211" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="1" t="n">
-        <v>44378</v>
-      </c>
-      <c r="B212" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C212" t="n">
-        <v>1.27554841074043</v>
-      </c>
-      <c r="D212" t="n">
-        <v>0.77883905480113</v>
-      </c>
-      <c r="E212" t="n">
-        <v>8.22526286317913</v>
-      </c>
-      <c r="F212" t="n">
-        <v>13.4709744052696</v>
-      </c>
-      <c r="G212" t="s">
-        <v>68</v>
-      </c>
-      <c r="H212" t="n">
-        <v>1</v>
-      </c>
-      <c r="I212" t="n">
-        <v>2</v>
-      </c>
-      <c r="J212" t="s">
-        <v>14</v>
-      </c>
-      <c r="K212" t="n">
-        <v>3.217</v>
-      </c>
-      <c r="L212" t="s">
-        <v>15</v>
-      </c>
-      <c r="M212" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="1" t="n">
-        <v>44409</v>
-      </c>
-      <c r="B213" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C213" t="n">
-        <v>1.27158946503466</v>
-      </c>
-      <c r="D213" t="n">
-        <v>0.77514515398221</v>
-      </c>
-      <c r="E213" t="n">
-        <v>8.25087126116166</v>
-      </c>
-      <c r="F213" t="n">
-        <v>13.535169405563</v>
-      </c>
-      <c r="G213" t="s">
-        <v>68</v>
-      </c>
-      <c r="H213" t="n">
-        <v>4</v>
-      </c>
-      <c r="I213" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J213" t="s">
-        <v>69</v>
-      </c>
-      <c r="K213" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="L213" t="s">
-        <v>15</v>
-      </c>
-      <c r="M213" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="1" t="n">
-        <v>44440</v>
-      </c>
-      <c r="B214" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C214" t="n">
-        <v>1.26765586403197</v>
-      </c>
-      <c r="D214" t="n">
-        <v>0.771480925777955</v>
-      </c>
-      <c r="E214" t="n">
-        <v>8.27647413682125</v>
-      </c>
-      <c r="F214" t="n">
-        <v>13.5994560882638</v>
-      </c>
-      <c r="G214" t="s">
-        <v>68</v>
-      </c>
-      <c r="H214" t="n">
-        <v>6</v>
-      </c>
-      <c r="I214" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J214" t="s">
-        <v>69</v>
-      </c>
-      <c r="K214" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="L214" t="s">
-        <v>15</v>
-      </c>
-      <c r="M214" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="1" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B215" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C215" t="n">
-        <v>1.26374731987251</v>
-      </c>
-      <c r="D215" t="n">
-        <v>0.767845995297327</v>
-      </c>
-      <c r="E215" t="n">
-        <v>8.30207178924731</v>
-      </c>
-      <c r="F215" t="n">
-        <v>13.6638349842377</v>
-      </c>
-      <c r="G215" t="s">
-        <v>68</v>
-      </c>
-      <c r="H215" t="n">
-        <v>2</v>
-      </c>
-      <c r="I215" t="n">
-        <v>1</v>
-      </c>
-      <c r="J215" t="s">
-        <v>14</v>
-      </c>
-      <c r="K215" t="n">
-        <v>1.616</v>
-      </c>
-      <c r="L215" t="s">
-        <v>15</v>
-      </c>
-      <c r="M215" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="1" t="n">
-        <v>44501</v>
-      </c>
-      <c r="B216" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C216" t="n">
-        <v>1.25986354964106</v>
-      </c>
-      <c r="D216" t="n">
-        <v>0.764239994429522</v>
-      </c>
-      <c r="E216" t="n">
-        <v>8.32766451258915</v>
-      </c>
-      <c r="F216" t="n">
-        <v>13.7283066177165</v>
-      </c>
-      <c r="G216" t="s">
-        <v>68</v>
-      </c>
-      <c r="H216" t="n">
-        <v>1</v>
-      </c>
-      <c r="I216" t="n">
-        <v>2</v>
-      </c>
-      <c r="J216" t="s">
-        <v>14</v>
-      </c>
-      <c r="K216" t="n">
-        <v>3.217</v>
-      </c>
-      <c r="L216" t="s">
-        <v>15</v>
-      </c>
-      <c r="M216" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="1" t="n">
-        <v>44531</v>
-      </c>
-      <c r="B217" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C217" t="n">
-        <v>1.25600427525195</v>
-      </c>
-      <c r="D217" t="n">
-        <v>0.76066256168165</v>
-      </c>
-      <c r="E217" t="n">
-        <v>8.35325259617117</v>
-      </c>
-      <c r="F217" t="n">
-        <v>13.792871506461</v>
-      </c>
-      <c r="G217" t="s">
-        <v>68</v>
-      </c>
-      <c r="H217" t="n">
-        <v>3</v>
-      </c>
-      <c r="I217" t="n">
-        <v>0</v>
-      </c>
-      <c r="J217" t="s">
-        <v>14</v>
-      </c>
-      <c r="K217" t="n">
-        <v>1.079</v>
-      </c>
-      <c r="L217" t="s">
-        <v>15</v>
-      </c>
-      <c r="M217" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="1" t="n">
-        <v>44562</v>
-      </c>
-      <c r="B218" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C218" t="n">
-        <v>1.2521692233373</v>
-      </c>
-      <c r="D218" t="n">
-        <v>0.757113342021273</v>
-      </c>
-      <c r="E218" t="n">
-        <v>8.37883632460457</v>
-      </c>
-      <c r="F218" t="n">
-        <v>13.8575301619181</v>
-      </c>
-      <c r="G218" t="s">
-        <v>68</v>
-      </c>
-      <c r="H218" t="n">
-        <v>1</v>
-      </c>
-      <c r="I218" t="n">
-        <v>2</v>
-      </c>
-      <c r="J218" t="s">
-        <v>14</v>
-      </c>
-      <c r="K218" t="n">
-        <v>3.217</v>
-      </c>
-      <c r="L218" t="s">
-        <v>15</v>
-      </c>
-      <c r="M218" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B219" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C219" t="n">
-        <v>1.24835812513854</v>
-      </c>
-      <c r="D219" t="n">
-        <v>0.753591986723628</v>
-      </c>
-      <c r="E219" t="n">
-        <v>8.4044159778958</v>
-      </c>
-      <c r="F219" t="n">
-        <v>13.9222830893744</v>
-      </c>
-      <c r="G219" t="s">
-        <v>68</v>
-      </c>
-      <c r="H219" t="n">
-        <v>1</v>
-      </c>
-      <c r="I219" t="n">
-        <v>2</v>
-      </c>
-      <c r="J219" t="s">
-        <v>14</v>
-      </c>
-      <c r="K219" t="n">
-        <v>3.217</v>
-      </c>
-      <c r="L219" t="s">
-        <v>15</v>
-      </c>
-      <c r="M219" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="B220" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C220" t="n">
-        <v>1.24457071640115</v>
-      </c>
-      <c r="D220" t="n">
-        <v>0.750098153223377</v>
-      </c>
-      <c r="E220" t="n">
-        <v>8.42999183155192</v>
-      </c>
-      <c r="F220" t="n">
-        <v>13.9871307881037</v>
-      </c>
-      <c r="G220" t="s">
-        <v>68</v>
-      </c>
-      <c r="H220" t="n">
-        <v>1</v>
-      </c>
-      <c r="I220" t="n">
-        <v>2</v>
-      </c>
-      <c r="J220" t="s">
-        <v>14</v>
-      </c>
-      <c r="K220" t="n">
-        <v>3.217</v>
-      </c>
-      <c r="L220" t="s">
-        <v>15</v>
-      </c>
-      <c r="M220" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="1" t="n">
-        <v>44652</v>
-      </c>
-      <c r="B221" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C221" t="n">
-        <v>1.24080673727232</v>
-      </c>
-      <c r="D221" t="n">
-        <v>0.746631504970702</v>
-      </c>
-      <c r="E221" t="n">
-        <v>8.45556415668283</v>
-      </c>
-      <c r="F221" t="n">
-        <v>14.0520737515116</v>
-      </c>
-      <c r="G221" t="s">
-        <v>68</v>
-      </c>
-      <c r="H221" t="n">
-        <v>2</v>
-      </c>
-      <c r="I221" t="n">
-        <v>1</v>
-      </c>
-      <c r="J221" t="s">
-        <v>14</v>
-      </c>
-      <c r="K221" t="n">
-        <v>1.616</v>
-      </c>
-      <c r="L221" t="s">
-        <v>15</v>
-      </c>
-      <c r="M221" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="1" t="n">
-        <v>44682</v>
-      </c>
-      <c r="B222" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C222" t="n">
-        <v>1.23706593220168</v>
-      </c>
-      <c r="D222" t="n">
-        <v>0.743191711291613</v>
-      </c>
-      <c r="E222" t="n">
-        <v>8.48113322010061</v>
-      </c>
-      <c r="F222" t="n">
-        <v>14.1171124672752</v>
-      </c>
-      <c r="G222" t="s">
-        <v>68</v>
-      </c>
-      <c r="H222" t="n">
-        <v>5</v>
-      </c>
-      <c r="I222" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J222" t="s">
-        <v>69</v>
-      </c>
-      <c r="K222" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="L222" t="s">
-        <v>15</v>
-      </c>
-      <c r="M222" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="B223" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C223" t="n">
-        <v>1.23334804984477</v>
-      </c>
-      <c r="D223" t="n">
-        <v>0.739778447252311</v>
-      </c>
-      <c r="E223" t="n">
-        <v>8.50669928441603</v>
-      </c>
-      <c r="F223" t="n">
-        <v>14.1822474174786</v>
-      </c>
-      <c r="G223" t="s">
-        <v>68</v>
-      </c>
-      <c r="H223" t="n">
-        <v>5</v>
-      </c>
-      <c r="I223" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J223" t="s">
-        <v>69</v>
-      </c>
-      <c r="K223" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="L223" t="s">
-        <v>15</v>
-      </c>
-      <c r="M223" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="1" t="n">
-        <v>44743</v>
-      </c>
-      <c r="B224" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C224" t="n">
-        <v>1.22965284296929</v>
-      </c>
-      <c r="D224" t="n">
-        <v>0.736391393527461</v>
-      </c>
-      <c r="E224" t="n">
-        <v>8.53226260813231</v>
-      </c>
-      <c r="F224" t="n">
-        <v>14.2474790787451</v>
-      </c>
-      <c r="G224" t="s">
-        <v>68</v>
-      </c>
-      <c r="H224" t="n">
-        <v>4</v>
-      </c>
-      <c r="I224" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J224" t="s">
-        <v>69</v>
-      </c>
-      <c r="K224" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="L224" t="s">
-        <v>15</v>
-      </c>
-      <c r="M224" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="1" t="n">
-        <v>44774</v>
-      </c>
-      <c r="B225" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C225" t="n">
-        <v>1.22598006836396</v>
-      </c>
-      <c r="D225" t="n">
-        <v>0.73303023627225</v>
-      </c>
-      <c r="E225" t="n">
-        <v>8.55782344573623</v>
-      </c>
-      <c r="F225" t="n">
-        <v>14.3128079223648</v>
-      </c>
-      <c r="G225" t="s">
-        <v>68</v>
-      </c>
-      <c r="H225" t="n">
-        <v>3</v>
-      </c>
-      <c r="I225" t="n">
-        <v>0</v>
-      </c>
-      <c r="J225" t="s">
-        <v>14</v>
-      </c>
-      <c r="K225" t="n">
-        <v>1.079</v>
-      </c>
-      <c r="L225" t="s">
-        <v>15</v>
-      </c>
-      <c r="M225" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="1" t="n">
-        <v>44805</v>
-      </c>
-      <c r="B226" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C226" t="n">
-        <v>1.22232948675002</v>
-      </c>
-      <c r="D226" t="n">
-        <v>0.729694666998091</v>
-      </c>
-      <c r="E226" t="n">
-        <v>8.5833820477867</v>
-      </c>
-      <c r="F226" t="n">
-        <v>14.3782344144196</v>
-      </c>
-      <c r="G226" t="s">
-        <v>68</v>
-      </c>
-      <c r="H226" t="n">
-        <v>0</v>
-      </c>
-      <c r="I226" t="n">
-        <v>3</v>
-      </c>
-      <c r="J226" t="s">
-        <v>14</v>
-      </c>
-      <c r="K226" t="n">
-        <v>324.909</v>
-      </c>
-      <c r="L226" t="s">
-        <v>41</v>
-      </c>
-      <c r="M226" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="1" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B227" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C227" t="n">
-        <v>1.21870086269504</v>
-      </c>
-      <c r="D227" t="n">
-        <v>0.726384382451847</v>
-      </c>
-      <c r="E227" t="n">
-        <v>8.60893866100088</v>
-      </c>
-      <c r="F227" t="n">
-        <v>14.4437590159036</v>
-      </c>
-      <c r="G227" t="s">
-        <v>68</v>
-      </c>
-      <c r="H227" t="n">
-        <v>2</v>
-      </c>
-      <c r="I227" t="n">
-        <v>1</v>
-      </c>
-      <c r="J227" t="s">
-        <v>14</v>
-      </c>
-      <c r="K227" t="n">
-        <v>1.616</v>
-      </c>
-      <c r="L227" t="s">
-        <v>15</v>
-      </c>
-      <c r="M227" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="B228" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C228" t="n">
-        <v>1.21509396452928</v>
-      </c>
-      <c r="D228" t="n">
-        <v>0.72309908449847</v>
-      </c>
-      <c r="E228" t="n">
-        <v>8.63449352833784</v>
-      </c>
-      <c r="F228" t="n">
-        <v>14.5093821828406</v>
-      </c>
-      <c r="G228" t="s">
-        <v>68</v>
-      </c>
-      <c r="H228" t="n">
-        <v>2</v>
-      </c>
-      <c r="I228" t="n">
-        <v>1</v>
-      </c>
-      <c r="J228" t="s">
-        <v>14</v>
-      </c>
-      <c r="K228" t="n">
-        <v>1.616</v>
-      </c>
-      <c r="L228" t="s">
-        <v>15</v>
-      </c>
-      <c r="M228" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="B229" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C229" t="n">
-        <v>1.21150856426425</v>
-      </c>
-      <c r="D229" t="n">
-        <v>0.719838480006911</v>
-      </c>
-      <c r="E229" t="n">
-        <v>8.66004688908005</v>
-      </c>
-      <c r="F229" t="n">
-        <v>14.5751043663986</v>
-      </c>
-      <c r="G229" t="s">
-        <v>68</v>
-      </c>
-      <c r="H229" t="n">
-        <v>3</v>
-      </c>
-      <c r="I229" t="n">
-        <v>0</v>
-      </c>
-      <c r="J229" t="s">
-        <v>14</v>
-      </c>
-      <c r="K229" t="n">
-        <v>1.079</v>
-      </c>
-      <c r="L229" t="s">
-        <v>15</v>
-      </c>
-      <c r="M229" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="1" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B230" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C230" t="n">
-        <v>1.20794443751352</v>
-      </c>
-      <c r="D230" t="n">
-        <v>0.716602280739228</v>
-      </c>
-      <c r="E230" t="n">
-        <v>8.68559897891249</v>
-      </c>
-      <c r="F230" t="n">
-        <v>14.6409260130005</v>
-      </c>
-      <c r="G230" t="s">
-        <v>68</v>
-      </c>
-      <c r="H230" t="n">
-        <v>3</v>
-      </c>
-      <c r="I230" t="n">
-        <v>0</v>
-      </c>
-      <c r="J230" t="s">
-        <v>14</v>
-      </c>
-      <c r="K230" t="n">
-        <v>1.079</v>
-      </c>
-      <c r="L230" t="s">
-        <v>15</v>
-      </c>
-      <c r="M230" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="1" t="n">
-        <v>44958</v>
-      </c>
-      <c r="B231" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C231" t="n">
-        <v>1.2044013634157</v>
-      </c>
-      <c r="D231" t="n">
-        <v>0.713390203242748</v>
-      </c>
-      <c r="E231" t="n">
-        <v>8.71115002999974</v>
-      </c>
-      <c r="F231" t="n">
-        <v>14.7068475644322</v>
-      </c>
-      <c r="G231" t="s">
-        <v>68</v>
-      </c>
-      <c r="H231" t="n">
-        <v>3</v>
-      </c>
-      <c r="I231" t="n">
-        <v>0</v>
-      </c>
-      <c r="J231" t="s">
-        <v>14</v>
-      </c>
-      <c r="K231" t="n">
-        <v>1.079</v>
-      </c>
-      <c r="L231" t="s">
-        <v>15</v>
-      </c>
-      <c r="M231" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="1" t="n">
-        <v>44986</v>
-      </c>
-      <c r="B232" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C232" t="n">
-        <v>1.20087912455951</v>
-      </c>
-      <c r="D232" t="n">
-        <v>0.710201968745206</v>
-      </c>
-      <c r="E232" t="n">
-        <v>8.7367002710609</v>
-      </c>
-      <c r="F232" t="n">
-        <v>14.7728694579478</v>
-      </c>
-      <c r="G232" t="s">
-        <v>68</v>
-      </c>
-      <c r="H232" t="n">
-        <v>6</v>
-      </c>
-      <c r="I232" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J232" t="s">
-        <v>69</v>
-      </c>
-      <c r="K232" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="L232" t="s">
-        <v>15</v>
-      </c>
-      <c r="M232" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="1" t="n">
-        <v>45017</v>
-      </c>
-      <c r="B233" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C233" t="n">
-        <v>1.1973775069108</v>
-      </c>
-      <c r="D233" t="n">
-        <v>0.70703730305276</v>
-      </c>
-      <c r="E233" t="n">
-        <v>8.76224992744251</v>
-      </c>
-      <c r="F233" t="n">
-        <v>14.8389921263709</v>
-      </c>
-      <c r="G233" t="s">
-        <v>68</v>
-      </c>
-      <c r="H233" t="n">
-        <v>4</v>
-      </c>
-      <c r="I233" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J233" t="s">
-        <v>69</v>
-      </c>
-      <c r="K233" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="L233" t="s">
-        <v>15</v>
-      </c>
-      <c r="M233" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="1" t="n">
-        <v>45047</v>
-      </c>
-      <c r="B234" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C234" t="n">
-        <v>1.19389629974161</v>
-      </c>
-      <c r="D234" t="n">
-        <v>0.703895936450768</v>
-      </c>
-      <c r="E234" t="n">
-        <v>8.78779922118957</v>
-      </c>
-      <c r="F234" t="n">
-        <v>14.905215998195</v>
-      </c>
-      <c r="G234" t="s">
-        <v>68</v>
-      </c>
-      <c r="H234" t="n">
-        <v>2</v>
-      </c>
-      <c r="I234" t="n">
-        <v>1</v>
-      </c>
-      <c r="J234" t="s">
-        <v>14</v>
-      </c>
-      <c r="K234" t="n">
-        <v>1.616</v>
-      </c>
-      <c r="L234" t="s">
-        <v>15</v>
-      </c>
-      <c r="M234" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="B235" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C235" t="n">
-        <v>1.19043529556106</v>
-      </c>
-      <c r="D235" t="n">
-        <v>0.700777603607269</v>
-      </c>
-      <c r="E235" t="n">
-        <v>8.81334837111464</v>
-      </c>
-      <c r="F235" t="n">
-        <v>14.9715414976792</v>
-      </c>
-      <c r="G235" t="s">
-        <v>68</v>
-      </c>
-      <c r="H235" t="n">
-        <v>4</v>
-      </c>
-      <c r="I235" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J235" t="s">
-        <v>69</v>
-      </c>
-      <c r="K235" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="L235" t="s">
-        <v>15</v>
-      </c>
-      <c r="M235" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="1" t="n">
-        <v>45108</v>
-      </c>
-      <c r="B236" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C236" t="n">
-        <v>1.18699429004807</v>
-      </c>
-      <c r="D236" t="n">
-        <v>0.697682043479045</v>
-      </c>
-      <c r="E236" t="n">
-        <v>8.83889759286506</v>
-      </c>
-      <c r="F236" t="n">
-        <v>15.037969044943</v>
-      </c>
-      <c r="G236" t="s">
-        <v>68</v>
-      </c>
-      <c r="H236" t="n">
-        <v>6</v>
-      </c>
-      <c r="I236" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J236" t="s">
-        <v>69</v>
-      </c>
-      <c r="K236" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="L236" t="s">
-        <v>15</v>
-      </c>
-      <c r="M236" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="B237" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C237" t="n">
-        <v>1.18357308198586</v>
-      </c>
-      <c r="D237" t="n">
-        <v>0.694608999220212</v>
-      </c>
-      <c r="E237" t="n">
-        <v>8.86444709898851</v>
-      </c>
-      <c r="F237" t="n">
-        <v>15.1044990560571</v>
-      </c>
-      <c r="G237" t="s">
-        <v>68</v>
-      </c>
-      <c r="H237" t="n">
-        <v>4</v>
-      </c>
-      <c r="I237" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J237" t="s">
-        <v>69</v>
-      </c>
-      <c r="K237" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="L237" t="s">
-        <v>15</v>
-      </c>
-      <c r="M237" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="1" t="n">
-        <v>45170</v>
-      </c>
-      <c r="B238" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C238" t="n">
-        <v>1.18017147319816</v>
-      </c>
-      <c r="D238" t="n">
-        <v>0.691558218093233</v>
-      </c>
-      <c r="E238" t="n">
-        <v>8.88999709899679</v>
-      </c>
-      <c r="F238" t="n">
-        <v>15.1711319431331</v>
-      </c>
-      <c r="G238" t="s">
-        <v>68</v>
-      </c>
-      <c r="H238" t="n">
-        <v>3</v>
-      </c>
-      <c r="I238" t="n">
-        <v>0</v>
-      </c>
-      <c r="J238" t="s">
-        <v>14</v>
-      </c>
-      <c r="K238" t="n">
-        <v>1.079</v>
-      </c>
-      <c r="L238" t="s">
-        <v>15</v>
-      </c>
-      <c r="M238" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="1" t="n">
-        <v>45200</v>
-      </c>
-      <c r="B239" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C239" t="n">
-        <v>1.17678926848708</v>
-      </c>
-      <c r="D239" t="n">
-        <v>0.688529451382296</v>
-      </c>
-      <c r="E239" t="n">
-        <v>8.91554779942795</v>
-      </c>
-      <c r="F239" t="n">
-        <v>15.2378681144099</v>
-      </c>
-      <c r="G239" t="s">
-        <v>68</v>
-      </c>
-      <c r="H239" t="n">
-        <v>7</v>
-      </c>
-      <c r="I239" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J239" t="s">
-        <v>69</v>
-      </c>
-      <c r="K239" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="L239" t="s">
-        <v>15</v>
-      </c>
-      <c r="M239" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="1" t="n">
-        <v>45231</v>
-      </c>
-      <c r="B240" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C240" t="n">
-        <v>1.17342627557256</v>
-      </c>
-      <c r="D240" t="n">
-        <v>0.685522454308967</v>
-      </c>
-      <c r="E240" t="n">
-        <v>8.94109940390683</v>
-      </c>
-      <c r="F240" t="n">
-        <v>15.3047079743383</v>
-      </c>
-      <c r="G240" t="s">
-        <v>68</v>
-      </c>
-      <c r="H240" t="n">
-        <v>4</v>
-      </c>
-      <c r="I240" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J240" t="s">
-        <v>69</v>
-      </c>
-      <c r="K240" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="L240" t="s">
-        <v>15</v>
-      </c>
-      <c r="M240" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="1" t="n">
-        <v>45261</v>
-      </c>
-      <c r="B241" t="n">
-        <v>3.23909261569509</v>
-      </c>
-      <c r="C241" t="n">
-        <v>1.17008230503341</v>
-      </c>
-      <c r="D241" t="n">
-        <v>0.682536985950052</v>
-      </c>
-      <c r="E241" t="n">
-        <v>8.96665211320403</v>
-      </c>
-      <c r="F241" t="n">
-        <v>15.3716519236632</v>
-      </c>
-      <c r="G241" t="s">
-        <v>68</v>
-      </c>
-      <c r="H241" t="n">
-        <v>1</v>
-      </c>
-      <c r="I241" t="n">
-        <v>2</v>
-      </c>
-      <c r="J241" t="s">
-        <v>14</v>
-      </c>
-      <c r="K241" t="n">
-        <v>3.217</v>
-      </c>
-      <c r="L241" t="s">
-        <v>15</v>
-      </c>
-      <c r="M241" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="B242" t="n">
-        <v>4.15144124236694</v>
-      </c>
-      <c r="C242" t="n">
-        <v>0.350558146617506</v>
-      </c>
-      <c r="D242" t="n">
-        <v>0.0979757331951868</v>
-      </c>
-      <c r="E242" t="n">
-        <v>55.8913921028939</v>
-      </c>
-      <c r="F242" t="n">
-        <v>190.937675558943</v>
-      </c>
-      <c r="G242" t="s">
-        <v>70</v>
-      </c>
-      <c r="H242" t="n">
-        <v>6</v>
-      </c>
-      <c r="I242" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J242" t="s">
-        <v>69</v>
-      </c>
-      <c r="K242" t="n">
-        <v>0.692</v>
-      </c>
-      <c r="L242" t="s">
-        <v>15</v>
-      </c>
-      <c r="M242" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="1" t="n">
-        <v>43862</v>
-      </c>
-      <c r="B243" t="n">
-        <v>3.21384524091082</v>
-      </c>
-      <c r="C243" t="n">
-        <v>0.243677725992583</v>
-      </c>
-      <c r="D243" t="n">
-        <v>0.0496694609263368</v>
-      </c>
-      <c r="E243" t="n">
-        <v>45.2639562319743</v>
-      </c>
-      <c r="F243" t="n">
-        <v>162.793885152477</v>
-      </c>
-      <c r="G243" t="s">
-        <v>70</v>
-      </c>
-      <c r="H243" t="n">
-        <v>6</v>
-      </c>
-      <c r="I243" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J243" t="s">
-        <v>69</v>
-      </c>
-      <c r="K243" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="L243" t="s">
-        <v>15</v>
-      </c>
-      <c r="M243" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="1" t="n">
-        <v>43891</v>
-      </c>
-      <c r="B244" t="n">
-        <v>2.58788826631676</v>
-      </c>
-      <c r="C244" t="n">
-        <v>0.187274280136378</v>
-      </c>
-      <c r="D244" t="n">
-        <v>0.0317060564688686</v>
-      </c>
-      <c r="E244" t="n">
-        <v>38.3056218015937</v>
-      </c>
-      <c r="F244" t="n">
-        <v>174.277512362199</v>
-      </c>
-      <c r="G244" t="s">
-        <v>70</v>
-      </c>
-      <c r="H244" t="n">
-        <v>3</v>
-      </c>
-      <c r="I244" t="n">
-        <v>0</v>
-      </c>
-      <c r="J244" t="s">
-        <v>69</v>
-      </c>
-      <c r="K244" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="L244" t="s">
-        <v>15</v>
-      </c>
-      <c r="M244" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="1" t="n">
-        <v>43922</v>
-      </c>
-      <c r="B245" t="n">
-        <v>3.93849165880519</v>
-      </c>
-      <c r="C245" t="n">
-        <v>0.268980597911201</v>
-      </c>
-      <c r="D245" t="n">
-        <v>0.0590520235898489</v>
-      </c>
-      <c r="E245" t="n">
-        <v>64.8440318478799</v>
-      </c>
-      <c r="F245" t="n">
-        <v>283.664368392095</v>
-      </c>
-      <c r="G245" t="s">
-        <v>70</v>
-      </c>
-      <c r="H245" t="n">
-        <v>2</v>
-      </c>
-      <c r="I245" t="n">
-        <v>2</v>
-      </c>
-      <c r="J245" t="s">
-        <v>14</v>
-      </c>
-      <c r="K245" t="n">
-        <v>1.964</v>
-      </c>
-      <c r="L245" t="s">
-        <v>15</v>
-      </c>
-      <c r="M245" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="1" t="n">
-        <v>43952</v>
-      </c>
-      <c r="B246" t="n">
-        <v>7.16636152412525</v>
-      </c>
-      <c r="C246" t="n">
-        <v>0.373395422836988</v>
-      </c>
-      <c r="D246" t="n">
-        <v>0.056800511450238</v>
-      </c>
-      <c r="E246" t="n">
-        <v>144.207671576106</v>
-      </c>
-      <c r="F246" t="n">
-        <v>552.962004835199</v>
-      </c>
-      <c r="G246" t="s">
-        <v>70</v>
-      </c>
-      <c r="H246" t="n">
-        <v>0</v>
-      </c>
-      <c r="I246" t="n">
-        <v>7</v>
-      </c>
-      <c r="J246" t="s">
-        <v>14</v>
-      </c>
-      <c r="K246" t="n">
-        <v>717.636</v>
-      </c>
-      <c r="L246" t="s">
-        <v>41</v>
-      </c>
-      <c r="M246" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="1" t="n">
-        <v>43983</v>
-      </c>
-      <c r="B247" t="n">
-        <v>4.38701759032416</v>
-      </c>
-      <c r="C247" t="n">
-        <v>0.167631831303683</v>
-      </c>
-      <c r="D247" t="n">
-        <v>0.032206187874718</v>
-      </c>
-      <c r="E247" t="n">
-        <v>96.7492568551902</v>
-      </c>
-      <c r="F247" t="n">
-        <v>320.719073594781</v>
-      </c>
-      <c r="G247" t="s">
-        <v>70</v>
-      </c>
-      <c r="H247" t="n">
-        <v>0</v>
-      </c>
-      <c r="I247" t="n">
-        <v>4</v>
-      </c>
-      <c r="J247" t="s">
-        <v>14</v>
-      </c>
-      <c r="K247" t="n">
-        <v>439.702</v>
-      </c>
-      <c r="L247" t="s">
-        <v>41</v>
-      </c>
-      <c r="M247" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="1" t="n">
-        <v>44013</v>
-      </c>
-      <c r="B248" t="n">
-        <v>4.20814317929731</v>
-      </c>
-      <c r="C248" t="n">
-        <v>0.178726069589562</v>
-      </c>
-      <c r="D248" t="n">
-        <v>0.0378660289389073</v>
-      </c>
-      <c r="E248" t="n">
-        <v>85.8871505655432</v>
-      </c>
-      <c r="F248" t="n">
-        <v>449.10511677606</v>
-      </c>
-      <c r="G248" t="s">
-        <v>70</v>
-      </c>
-      <c r="H248" t="n">
-        <v>1</v>
-      </c>
-      <c r="I248" t="n">
-        <v>3</v>
-      </c>
-      <c r="J248" t="s">
-        <v>14</v>
-      </c>
-      <c r="K248" t="n">
-        <v>4.176</v>
-      </c>
-      <c r="L248" t="s">
-        <v>15</v>
-      </c>
-      <c r="M248" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="1" t="n">
-        <v>44044</v>
-      </c>
-      <c r="B249" t="n">
-        <v>4.30271482536286</v>
-      </c>
-      <c r="C249" t="n">
-        <v>0.143830693035048</v>
-      </c>
-      <c r="D249" t="n">
-        <v>0.0190812907138846</v>
-      </c>
-      <c r="E249" t="n">
-        <v>112.605618511568</v>
-      </c>
-      <c r="F249" t="n">
-        <v>503.266395093218</v>
-      </c>
-      <c r="G249" t="s">
-        <v>70</v>
-      </c>
-      <c r="H249" t="n">
-        <v>0</v>
-      </c>
-      <c r="I249" t="n">
-        <v>4</v>
-      </c>
-      <c r="J249" t="s">
-        <v>14</v>
-      </c>
-      <c r="K249" t="n">
-        <v>431.271</v>
-      </c>
-      <c r="L249" t="s">
-        <v>41</v>
-      </c>
-      <c r="M249" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="1" t="n">
-        <v>44075</v>
-      </c>
-      <c r="B250" t="n">
-        <v>2.70004733570733</v>
-      </c>
-      <c r="C250" t="n">
-        <v>0.0840885144360343</v>
-      </c>
-      <c r="D250" t="n">
-        <v>0.0115996966425807</v>
-      </c>
-      <c r="E250" t="n">
-        <v>73.468464930473</v>
-      </c>
-      <c r="F250" t="n">
-        <v>372.162515781149</v>
-      </c>
-      <c r="G250" t="s">
-        <v>70</v>
-      </c>
-      <c r="H250" t="n">
-        <v>0</v>
-      </c>
-      <c r="I250" t="n">
-        <v>3</v>
-      </c>
-      <c r="J250" t="s">
-        <v>14</v>
-      </c>
-      <c r="K250" t="n">
-        <v>271.005</v>
-      </c>
-      <c r="L250" t="s">
-        <v>41</v>
-      </c>
-      <c r="M250" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="1" t="n">
-        <v>44105</v>
-      </c>
-      <c r="B251" t="n">
-        <v>4.92319892347782</v>
-      </c>
-      <c r="C251" t="n">
-        <v>0.144894147234522</v>
-      </c>
-      <c r="D251" t="n">
-        <v>0.0260941778661215</v>
-      </c>
-      <c r="E251" t="n">
-        <v>161.375800601061</v>
-      </c>
-      <c r="F251" t="n">
-        <v>1016.75854517356</v>
-      </c>
-      <c r="G251" t="s">
-        <v>70</v>
-      </c>
-      <c r="H251" t="n">
-        <v>2</v>
-      </c>
-      <c r="I251" t="n">
-        <v>3</v>
-      </c>
-      <c r="J251" t="s">
-        <v>14</v>
-      </c>
-      <c r="K251" t="n">
-        <v>2.454</v>
-      </c>
-      <c r="L251" t="s">
-        <v>15</v>
-      </c>
-      <c r="M251" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="1" t="n">
-        <v>44136</v>
-      </c>
-      <c r="B252" t="n">
-        <v>5.45020567035955</v>
-      </c>
-      <c r="C252" t="n">
-        <v>0.160514101761841</v>
-      </c>
-      <c r="D252" t="n">
-        <v>0.0196056019953771</v>
-      </c>
-      <c r="E252" t="n">
-        <v>190.114878029318</v>
-      </c>
-      <c r="F252" t="n">
-        <v>1524.46438683339</v>
-      </c>
-      <c r="G252" t="s">
-        <v>70</v>
-      </c>
-      <c r="H252" t="n">
-        <v>0</v>
-      </c>
-      <c r="I252" t="n">
-        <v>5</v>
-      </c>
-      <c r="J252" t="s">
-        <v>14</v>
-      </c>
-      <c r="K252" t="n">
-        <v>546.021</v>
-      </c>
-      <c r="L252" t="s">
-        <v>41</v>
-      </c>
-      <c r="M252" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>44166</v>
-      </c>
-      <c r="B253" t="n">
-        <v>5.7306534942796</v>
-      </c>
-      <c r="C253" t="n">
-        <v>0.156523813803623</v>
-      </c>
-      <c r="D253" t="n">
-        <v>0.013862407532154</v>
-      </c>
-      <c r="E253" t="n">
-        <v>225.828293183365</v>
-      </c>
-      <c r="F253" t="n">
-        <v>1743.4335871736</v>
-      </c>
-      <c r="G253" t="s">
-        <v>70</v>
-      </c>
-      <c r="H253" t="n">
-        <v>2</v>
-      </c>
-      <c r="I253" t="n">
-        <v>4</v>
-      </c>
-      <c r="J253" t="s">
-        <v>14</v>
-      </c>
-      <c r="K253" t="n">
-        <v>2.856</v>
-      </c>
-      <c r="L253" t="s">
-        <v>15</v>
-      </c>
-      <c r="M253" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="1" t="n">
-        <v>44197</v>
-      </c>
-      <c r="B254" t="n">
-        <v>3.87002257682594</v>
-      </c>
-      <c r="C254" t="n">
-        <v>0.0794867978657022</v>
-      </c>
-      <c r="D254" t="n">
-        <v>0.00398193103003322</v>
-      </c>
-      <c r="E254" t="n">
-        <v>205.396223682953</v>
-      </c>
-      <c r="F254" t="n">
-        <v>1640.09248874685</v>
-      </c>
-      <c r="G254" t="s">
-        <v>70</v>
-      </c>
-      <c r="H254" t="n">
-        <v>0</v>
-      </c>
-      <c r="I254" t="n">
-        <v>4</v>
-      </c>
-      <c r="J254" t="s">
-        <v>14</v>
-      </c>
-      <c r="K254" t="n">
-        <v>388.002</v>
-      </c>
-      <c r="L254" t="s">
-        <v>41</v>
-      </c>
-      <c r="M254" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="1" t="n">
-        <v>44228</v>
-      </c>
-      <c r="B255" t="n">
-        <v>2.63411186497751</v>
-      </c>
-      <c r="C255" t="n">
-        <v>0.0471276910153888</v>
-      </c>
-      <c r="D255" t="n">
-        <v>0.00317899652907004</v>
-      </c>
-      <c r="E255" t="n">
-        <v>127.60422365954</v>
-      </c>
-      <c r="F255" t="n">
-        <v>1951.95957673009</v>
-      </c>
-      <c r="G255" t="s">
-        <v>70</v>
-      </c>
-      <c r="H255" t="n">
-        <v>1</v>
-      </c>
-      <c r="I255" t="n">
-        <v>2</v>
-      </c>
-      <c r="J255" t="s">
-        <v>14</v>
-      </c>
-      <c r="K255" t="n">
-        <v>2.618</v>
-      </c>
-      <c r="L255" t="s">
-        <v>15</v>
-      </c>
-      <c r="M255" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="1" t="n">
-        <v>44256</v>
-      </c>
-      <c r="B256" t="n">
-        <v>2.5027042403012</v>
-      </c>
-      <c r="C256" t="n">
-        <v>0.0384138227775951</v>
-      </c>
-      <c r="D256" t="n">
-        <v>0.002194542129541</v>
-      </c>
-      <c r="E256" t="n">
-        <v>147.591213928859</v>
-      </c>
-      <c r="F256" t="n">
-        <v>842.398646856422</v>
-      </c>
-      <c r="G256" t="s">
-        <v>70</v>
-      </c>
-      <c r="H256" t="n">
-        <v>1</v>
-      </c>
-      <c r="I256" t="n">
-        <v>2</v>
-      </c>
-      <c r="J256" t="s">
-        <v>14</v>
-      </c>
-      <c r="K256" t="n">
-        <v>2.488</v>
-      </c>
-      <c r="L256" t="s">
-        <v>15</v>
-      </c>
-      <c r="M256" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="1" t="n">
-        <v>44287</v>
-      </c>
-      <c r="B257" t="n">
-        <v>3.36143398917541</v>
-      </c>
-      <c r="C257" t="n">
-        <v>0.0329691509717375</v>
-      </c>
-      <c r="D257" t="n">
-        <v>0.00367033514519426</v>
-      </c>
-      <c r="E257" t="n">
-        <v>290.443856299554</v>
-      </c>
-      <c r="F257" t="n">
-        <v>2918.27406804792</v>
-      </c>
-      <c r="G257" t="s">
-        <v>70</v>
-      </c>
-      <c r="H257" t="n">
-        <v>2</v>
-      </c>
-      <c r="I257" t="n">
-        <v>1</v>
-      </c>
-      <c r="J257" t="s">
-        <v>14</v>
-      </c>
-      <c r="K257" t="n">
-        <v>1.677</v>
-      </c>
-      <c r="L257" t="s">
-        <v>15</v>
-      </c>
-      <c r="M257" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="1" t="n">
-        <v>44317</v>
-      </c>
-      <c r="B258" t="n">
-        <v>5.86374558739355</v>
-      </c>
-      <c r="C258" t="n">
-        <v>0.0674428850402894</v>
-      </c>
-      <c r="D258" t="n">
-        <v>0.0025666977823155</v>
-      </c>
-      <c r="E258" t="n">
-        <v>494.325316808426</v>
-      </c>
-      <c r="F258" t="n">
-        <v>5610.24864173134</v>
-      </c>
-      <c r="G258" t="s">
-        <v>70</v>
-      </c>
-      <c r="H258" t="n">
-        <v>2</v>
-      </c>
-      <c r="I258" t="n">
-        <v>4</v>
-      </c>
-      <c r="J258" t="s">
-        <v>14</v>
-      </c>
-      <c r="K258" t="n">
-        <v>2.922</v>
-      </c>
-      <c r="L258" t="s">
-        <v>15</v>
-      </c>
-      <c r="M258" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="1" t="n">
-        <v>44348</v>
-      </c>
-      <c r="B259" t="n">
-        <v>3.87367051019729</v>
-      </c>
-      <c r="C259" t="n">
-        <v>0.0268721035561538</v>
-      </c>
-      <c r="D259" t="n">
-        <v>0.000915970499505459</v>
-      </c>
-      <c r="E259" t="n">
-        <v>426.671416435583</v>
-      </c>
-      <c r="F259" t="n">
-        <v>3866.47328183278</v>
-      </c>
-      <c r="G259" t="s">
-        <v>70</v>
-      </c>
-      <c r="H259" t="n">
-        <v>1</v>
-      </c>
-      <c r="I259" t="n">
-        <v>3</v>
-      </c>
-      <c r="J259" t="s">
-        <v>14</v>
-      </c>
-      <c r="K259" t="n">
-        <v>3.845</v>
-      </c>
-      <c r="L259" t="s">
-        <v>15</v>
-      </c>
-      <c r="M259" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="1" t="n">
-        <v>44378</v>
-      </c>
-      <c r="B260" t="n">
-        <v>3.28751947231608</v>
-      </c>
-      <c r="C260" t="n">
-        <v>0.0231198488050841</v>
-      </c>
-      <c r="D260" t="n">
-        <v>0.00094783142563207</v>
-      </c>
-      <c r="E260" t="n">
-        <v>374.044627306051</v>
-      </c>
-      <c r="F260" t="n">
-        <v>4472.56401953988</v>
-      </c>
-      <c r="G260" t="s">
-        <v>70</v>
-      </c>
-      <c r="H260" t="n">
-        <v>0</v>
-      </c>
-      <c r="I260" t="n">
-        <v>3</v>
-      </c>
-      <c r="J260" t="s">
-        <v>14</v>
-      </c>
-      <c r="K260" t="n">
-        <v>329.752</v>
-      </c>
-      <c r="L260" t="s">
-        <v>41</v>
-      </c>
-      <c r="M260" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="1" t="n">
-        <v>44409</v>
-      </c>
-      <c r="B261" t="n">
-        <v>4.08303543519129</v>
-      </c>
-      <c r="C261" t="n">
-        <v>0.0277763367871512</v>
-      </c>
-      <c r="D261" t="n">
-        <v>0.000853544535180806</v>
-      </c>
-      <c r="E261" t="n">
-        <v>704.924961611237</v>
-      </c>
-      <c r="F261" t="n">
-        <v>6353.18676068567</v>
-      </c>
-      <c r="G261" t="s">
-        <v>70</v>
-      </c>
-      <c r="H261" t="n">
-        <v>0</v>
-      </c>
-      <c r="I261" t="n">
-        <v>4</v>
-      </c>
-      <c r="J261" t="s">
-        <v>14</v>
-      </c>
-      <c r="K261" t="n">
-        <v>409.304</v>
-      </c>
-      <c r="L261" t="s">
-        <v>41</v>
-      </c>
-      <c r="M261" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="1" t="n">
-        <v>44440</v>
-      </c>
-      <c r="B262" t="n">
-        <v>2.45194562893679</v>
-      </c>
-      <c r="C262" t="n">
-        <v>0.0151550180629164</v>
-      </c>
-      <c r="D262" t="n">
-        <v>0.000313510431239927</v>
-      </c>
-      <c r="E262" t="n">
-        <v>448.32308946203</v>
-      </c>
-      <c r="F262" t="n">
-        <v>6058.45354111356</v>
-      </c>
-      <c r="G262" t="s">
-        <v>70</v>
-      </c>
-      <c r="H262" t="n">
-        <v>1</v>
-      </c>
-      <c r="I262" t="n">
-        <v>1</v>
-      </c>
-      <c r="J262" t="s">
-        <v>14</v>
-      </c>
-      <c r="K262" t="n">
-        <v>2.438</v>
-      </c>
-      <c r="L262" t="s">
-        <v>15</v>
-      </c>
-      <c r="M262" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="1" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B263" t="n">
-        <v>4.09638100075874</v>
-      </c>
-      <c r="C263" t="n">
-        <v>0.0195278688591145</v>
-      </c>
-      <c r="D263" t="n">
-        <v>0.000235666319569948</v>
-      </c>
-      <c r="E263" t="n">
-        <v>883.268667278687</v>
-      </c>
-      <c r="F263" t="n">
-        <v>8133.18007703438</v>
-      </c>
-      <c r="G263" t="s">
-        <v>70</v>
-      </c>
-      <c r="H263" t="n">
-        <v>0</v>
-      </c>
-      <c r="I263" t="n">
-        <v>4</v>
-      </c>
-      <c r="J263" t="s">
-        <v>14</v>
-      </c>
-      <c r="K263" t="n">
-        <v>410.638</v>
-      </c>
-      <c r="L263" t="s">
-        <v>41</v>
-      </c>
-      <c r="M263" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="1" t="n">
-        <v>44501</v>
-      </c>
-      <c r="B264" t="n">
-        <v>5.34227425929349</v>
-      </c>
-      <c r="C264" t="n">
-        <v>0.0204278792707711</v>
-      </c>
-      <c r="D264" t="n">
-        <v>0.00038377339994859</v>
-      </c>
-      <c r="E264" t="n">
-        <v>1100.98427031074</v>
-      </c>
-      <c r="F264" t="n">
-        <v>14111.7199202492</v>
-      </c>
-      <c r="G264" t="s">
-        <v>70</v>
-      </c>
-      <c r="H264" t="n">
-        <v>0</v>
-      </c>
-      <c r="I264" t="n">
-        <v>5</v>
-      </c>
-      <c r="J264" t="s">
-        <v>14</v>
-      </c>
-      <c r="K264" t="n">
-        <v>535.227</v>
-      </c>
-      <c r="L264" t="s">
-        <v>41</v>
-      </c>
-      <c r="M264" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="1" t="n">
-        <v>44531</v>
-      </c>
-      <c r="B265" t="n">
-        <v>4.94475099262368</v>
-      </c>
-      <c r="C265" t="n">
-        <v>0.014828828487169</v>
-      </c>
-      <c r="D265" t="n">
-        <v>0.00037049140459367</v>
-      </c>
-      <c r="E265" t="n">
-        <v>1103.59256360018</v>
-      </c>
-      <c r="F265" t="n">
-        <v>27784.9289655374</v>
-      </c>
-      <c r="G265" t="s">
-        <v>70</v>
-      </c>
-      <c r="H265" t="n">
-        <v>0</v>
-      </c>
-      <c r="I265" t="n">
-        <v>5</v>
-      </c>
-      <c r="J265" t="s">
-        <v>14</v>
-      </c>
-      <c r="K265" t="n">
-        <v>495.475</v>
-      </c>
-      <c r="L265" t="s">
-        <v>41</v>
-      </c>
-      <c r="M265" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="1" t="n">
-        <v>44562</v>
-      </c>
-      <c r="B266" t="n">
-        <v>3.22267438952158</v>
-      </c>
-      <c r="C266" t="n">
-        <v>0.00872382765494203</v>
-      </c>
-      <c r="D266" t="n">
-        <v>0.000124863844490333</v>
-      </c>
-      <c r="E266" t="n">
-        <v>947.206404996592</v>
-      </c>
-      <c r="F266" t="n">
-        <v>20142.3001818713</v>
-      </c>
-      <c r="G266" t="s">
-        <v>70</v>
-      </c>
-      <c r="H266" t="n">
-        <v>0</v>
-      </c>
-      <c r="I266" t="n">
-        <v>3</v>
-      </c>
-      <c r="J266" t="s">
-        <v>14</v>
-      </c>
-      <c r="K266" t="n">
-        <v>323.267</v>
-      </c>
-      <c r="L266" t="s">
-        <v>41</v>
-      </c>
-      <c r="M266" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B267" t="n">
-        <v>2.09779356881313</v>
-      </c>
-      <c r="C267" t="n">
-        <v>0.00385916235781493</v>
-      </c>
-      <c r="D267" t="n">
-        <v>0.0000707611006517695</v>
-      </c>
-      <c r="E267" t="n">
-        <v>704.242294539276</v>
-      </c>
-      <c r="F267" t="n">
-        <v>19199.8531555976</v>
-      </c>
-      <c r="G267" t="s">
-        <v>70</v>
-      </c>
-      <c r="H267" t="n">
-        <v>1</v>
-      </c>
-      <c r="I267" t="n">
-        <v>1</v>
-      </c>
-      <c r="J267" t="s">
-        <v>14</v>
-      </c>
-      <c r="K267" t="n">
-        <v>2.087</v>
-      </c>
-      <c r="L267" t="s">
-        <v>15</v>
-      </c>
-      <c r="M267" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="B268" t="n">
-        <v>2.15546518046809</v>
-      </c>
-      <c r="C268" t="n">
-        <v>0.00649934532547522</v>
-      </c>
-      <c r="D268" t="n">
-        <v>0.0000580960951035039</v>
-      </c>
-      <c r="E268" t="n">
-        <v>1101.15494185616</v>
-      </c>
-      <c r="F268" t="n">
-        <v>17169.98009663</v>
-      </c>
-      <c r="G268" t="s">
-        <v>70</v>
-      </c>
-      <c r="H268" t="n">
-        <v>1</v>
-      </c>
-      <c r="I268" t="n">
-        <v>1</v>
-      </c>
-      <c r="J268" t="s">
-        <v>14</v>
-      </c>
-      <c r="K268" t="n">
-        <v>2.144</v>
-      </c>
-      <c r="L268" t="s">
-        <v>15</v>
-      </c>
-      <c r="M268" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="1" t="n">
-        <v>44652</v>
-      </c>
-      <c r="B269" t="n">
-        <v>2.71673685585897</v>
-      </c>
-      <c r="C269" t="n">
-        <v>0.003637256136757</v>
-      </c>
-      <c r="D269" t="n">
-        <v>0.000033076159863078</v>
-      </c>
-      <c r="E269" t="n">
-        <v>1517.1343812375</v>
-      </c>
-      <c r="F269" t="n">
-        <v>39762.8994762008</v>
-      </c>
-      <c r="G269" t="s">
-        <v>70</v>
-      </c>
-      <c r="H269" t="n">
-        <v>0</v>
-      </c>
-      <c r="I269" t="n">
-        <v>3</v>
-      </c>
-      <c r="J269" t="s">
-        <v>14</v>
-      </c>
-      <c r="K269" t="n">
-        <v>272.674</v>
-      </c>
-      <c r="L269" t="s">
-        <v>41</v>
-      </c>
-      <c r="M269" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="1" t="n">
-        <v>44682</v>
-      </c>
-      <c r="B270" t="n">
-        <v>5.12266012135095</v>
-      </c>
-      <c r="C270" t="n">
-        <v>0.0101362904754954</v>
-      </c>
-      <c r="D270" t="n">
-        <v>0.0000511368681358852</v>
-      </c>
-      <c r="E270" t="n">
-        <v>3565.58886108044</v>
-      </c>
-      <c r="F270" t="n">
-        <v>73494.5077344277</v>
-      </c>
-      <c r="G270" t="s">
-        <v>70</v>
-      </c>
-      <c r="H270" t="n">
-        <v>0</v>
-      </c>
-      <c r="I270" t="n">
-        <v>5</v>
-      </c>
-      <c r="J270" t="s">
-        <v>14</v>
-      </c>
-      <c r="K270" t="n">
-        <v>513.266</v>
-      </c>
-      <c r="L270" t="s">
-        <v>41</v>
-      </c>
-      <c r="M270" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="B271" t="n">
-        <v>3.50621163196978</v>
-      </c>
-      <c r="C271" t="n">
-        <v>0.00340139891820332</v>
-      </c>
-      <c r="D271" t="n">
-        <v>0.0000490176185456183</v>
-      </c>
-      <c r="E271" t="n">
-        <v>2538.92925979674</v>
-      </c>
-      <c r="F271" t="n">
-        <v>56981.538879821</v>
-      </c>
-      <c r="G271" t="s">
-        <v>70</v>
-      </c>
-      <c r="H271" t="n">
-        <v>1</v>
-      </c>
-      <c r="I271" t="n">
-        <v>3</v>
-      </c>
-      <c r="J271" t="s">
-        <v>14</v>
-      </c>
-      <c r="K271" t="n">
-        <v>3.481</v>
-      </c>
-      <c r="L271" t="s">
-        <v>15</v>
-      </c>
-      <c r="M271" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="1" t="n">
-        <v>44743</v>
-      </c>
-      <c r="B272" t="n">
-        <v>2.76370300317494</v>
-      </c>
-      <c r="C272" t="n">
-        <v>0.00282478368911472</v>
-      </c>
-      <c r="D272" t="n">
-        <v>0.0000118306279515635</v>
-      </c>
-      <c r="E272" t="n">
-        <v>2185.4662820558</v>
-      </c>
-      <c r="F272" t="n">
-        <v>101911.992586798</v>
-      </c>
-      <c r="G272" t="s">
-        <v>70</v>
-      </c>
-      <c r="H272" t="n">
-        <v>1</v>
-      </c>
-      <c r="I272" t="n">
-        <v>2</v>
-      </c>
-      <c r="J272" t="s">
-        <v>14</v>
-      </c>
-      <c r="K272" t="n">
-        <v>2.746</v>
-      </c>
-      <c r="L272" t="s">
-        <v>15</v>
-      </c>
-      <c r="M272" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="1" t="n">
-        <v>44774</v>
-      </c>
-      <c r="B273" t="n">
-        <v>2.79069215552232</v>
-      </c>
-      <c r="C273" t="n">
-        <v>0.00362987860470688</v>
-      </c>
-      <c r="D273" t="n">
-        <v>0.0000286199874016841</v>
-      </c>
-      <c r="E273" t="n">
-        <v>2409.67121869779</v>
-      </c>
-      <c r="F273" t="n">
-        <v>102789.496980047</v>
-      </c>
-      <c r="G273" t="s">
-        <v>70</v>
-      </c>
-      <c r="H273" t="n">
-        <v>8</v>
-      </c>
-      <c r="I273" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J273" t="s">
-        <v>69</v>
-      </c>
-      <c r="K273" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="L273" t="s">
-        <v>15</v>
-      </c>
-      <c r="M273" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="1" t="n">
-        <v>44805</v>
-      </c>
-      <c r="B274" t="n">
-        <v>1.93506546808299</v>
-      </c>
-      <c r="C274" t="n">
-        <v>0.00163355670269506</v>
-      </c>
-      <c r="D274" t="n">
-        <v>0.00000348123810994103</v>
-      </c>
-      <c r="E274" t="n">
-        <v>2299.54912563545</v>
-      </c>
-      <c r="F274" t="n">
-        <v>83895.1769502744</v>
-      </c>
-      <c r="G274" t="s">
-        <v>70</v>
-      </c>
-      <c r="H274" t="n">
-        <v>3</v>
-      </c>
-      <c r="I274" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J274" t="s">
-        <v>69</v>
-      </c>
-      <c r="K274" t="n">
-        <v>0.646</v>
-      </c>
-      <c r="L274" t="s">
-        <v>15</v>
-      </c>
-      <c r="M274" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="1" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B275" t="n">
-        <v>3.82451844734211</v>
-      </c>
-      <c r="C275" t="n">
-        <v>0.00256861148051868</v>
-      </c>
-      <c r="D275" t="n">
-        <v>0.00000314005578227842</v>
-      </c>
-      <c r="E275" t="n">
-        <v>8435.28570761685</v>
-      </c>
-      <c r="F275" t="n">
-        <v>346927.456071427</v>
-      </c>
-      <c r="G275" t="s">
-        <v>70</v>
-      </c>
-      <c r="H275" t="n">
-        <v>1</v>
-      </c>
-      <c r="I275" t="n">
-        <v>3</v>
-      </c>
-      <c r="J275" t="s">
-        <v>14</v>
-      </c>
-      <c r="K275" t="n">
-        <v>3.797</v>
-      </c>
-      <c r="L275" t="s">
-        <v>15</v>
-      </c>
-      <c r="M275" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="B276" t="n">
-        <v>4.58449476289281</v>
-      </c>
-      <c r="C276" t="n">
-        <v>0.0040875334872431</v>
-      </c>
-      <c r="D276" t="n">
-        <v>0.00000563570050680405</v>
-      </c>
-      <c r="E276" t="n">
-        <v>6508.70279761523</v>
-      </c>
-      <c r="F276" t="n">
-        <v>538624.409442522</v>
-      </c>
-      <c r="G276" t="s">
-        <v>70</v>
-      </c>
-      <c r="H276" t="n">
-        <v>3</v>
-      </c>
-      <c r="I276" t="n">
-        <v>2</v>
-      </c>
-      <c r="J276" t="s">
-        <v>14</v>
-      </c>
-      <c r="K276" t="n">
-        <v>1.526</v>
-      </c>
-      <c r="L276" t="s">
-        <v>15</v>
-      </c>
-      <c r="M276" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="B277" t="n">
-        <v>4.30362602825536</v>
-      </c>
-      <c r="C277" t="n">
-        <v>0.00167601319964979</v>
-      </c>
-      <c r="D277" t="n">
-        <v>0.00000396284446099903</v>
-      </c>
-      <c r="E277" t="n">
-        <v>9392.69901216338</v>
-      </c>
-      <c r="F277" t="n">
-        <v>562642.477848148</v>
-      </c>
-      <c r="G277" t="s">
-        <v>70</v>
-      </c>
-      <c r="H277" t="n">
-        <v>0</v>
-      </c>
-      <c r="I277" t="n">
-        <v>4</v>
-      </c>
-      <c r="J277" t="s">
-        <v>14</v>
-      </c>
-      <c r="K277" t="n">
-        <v>431.363</v>
-      </c>
-      <c r="L277" t="s">
-        <v>41</v>
-      </c>
-      <c r="M277" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="1" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B278" t="n">
-        <v>2.54231926393306</v>
-      </c>
-      <c r="C278" t="n">
-        <v>0.000912325445389379</v>
-      </c>
-      <c r="D278" t="n">
-        <v>0.000000987461299840848</v>
-      </c>
-      <c r="E278" t="n">
-        <v>3945.40177162604</v>
-      </c>
-      <c r="F278" t="n">
-        <v>527317.07651207</v>
-      </c>
-      <c r="G278" t="s">
-        <v>70</v>
-      </c>
-      <c r="H278" t="n">
-        <v>4</v>
-      </c>
-      <c r="I278" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J278" t="s">
-        <v>69</v>
-      </c>
-      <c r="K278" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="L278" t="s">
-        <v>15</v>
-      </c>
-      <c r="M278" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="1" t="n">
-        <v>44958</v>
-      </c>
-      <c r="B279" t="n">
-        <v>2.07910252026403</v>
-      </c>
-      <c r="C279" t="n">
-        <v>0.000509290155354747</v>
-      </c>
-      <c r="D279" t="n">
-        <v>0.000000729434583762631</v>
-      </c>
-      <c r="E279" t="n">
-        <v>5243.89830492339</v>
-      </c>
-      <c r="F279" t="n">
-        <v>930581.846361079</v>
-      </c>
-      <c r="G279" t="s">
-        <v>70</v>
-      </c>
-      <c r="H279" t="n">
-        <v>1</v>
-      </c>
-      <c r="I279" t="n">
-        <v>1</v>
-      </c>
-      <c r="J279" t="s">
-        <v>14</v>
-      </c>
-      <c r="K279" t="n">
-        <v>2.068</v>
-      </c>
-      <c r="L279" t="s">
-        <v>15</v>
-      </c>
-      <c r="M279" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="1" t="n">
-        <v>44986</v>
-      </c>
-      <c r="B280" t="n">
-        <v>2.18325848673687</v>
-      </c>
-      <c r="C280" t="n">
-        <v>0.000475947670018521</v>
-      </c>
-      <c r="D280" t="n">
-        <v>0.000000768016346597675</v>
-      </c>
-      <c r="E280" t="n">
-        <v>5841.59782765868</v>
-      </c>
-      <c r="F280" t="n">
-        <v>2002214.72461751</v>
-      </c>
-      <c r="G280" t="s">
-        <v>70</v>
-      </c>
-      <c r="H280" t="n">
-        <v>4</v>
-      </c>
-      <c r="I280" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J280" t="s">
-        <v>69</v>
-      </c>
-      <c r="K280" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="L280" t="s">
-        <v>15</v>
-      </c>
-      <c r="M280" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="1" t="n">
-        <v>45017</v>
-      </c>
-      <c r="B281" t="n">
-        <v>2.71863750401366</v>
-      </c>
-      <c r="C281" t="n">
-        <v>0.000625507646674496</v>
-      </c>
-      <c r="D281" t="n">
-        <v>0.000000733421770661873</v>
-      </c>
-      <c r="E281" t="n">
-        <v>11541.4154141455</v>
-      </c>
-      <c r="F281" t="n">
-        <v>1200003.95769351</v>
-      </c>
-      <c r="G281" t="s">
-        <v>70</v>
-      </c>
-      <c r="H281" t="n">
-        <v>0</v>
-      </c>
-      <c r="I281" t="n">
-        <v>3</v>
-      </c>
-      <c r="J281" t="s">
-        <v>14</v>
-      </c>
-      <c r="K281" t="n">
-        <v>272.864</v>
-      </c>
-      <c r="L281" t="s">
-        <v>41</v>
-      </c>
-      <c r="M281" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="1" t="n">
-        <v>45047</v>
-      </c>
-      <c r="B282" t="n">
-        <v>5.00775760067976</v>
-      </c>
-      <c r="C282" t="n">
-        <v>0.00106721717842979</v>
-      </c>
-      <c r="D282" t="n">
-        <v>0.000000484280450449679</v>
-      </c>
-      <c r="E282" t="n">
-        <v>21177.7297269856</v>
-      </c>
-      <c r="F282" t="n">
-        <v>1674785.13987038</v>
-      </c>
-      <c r="G282" t="s">
-        <v>70</v>
-      </c>
-      <c r="H282" t="n">
-        <v>1</v>
-      </c>
-      <c r="I282" t="n">
-        <v>4</v>
-      </c>
-      <c r="J282" t="s">
-        <v>14</v>
-      </c>
-      <c r="K282" t="n">
-        <v>4.968</v>
-      </c>
-      <c r="L282" t="s">
-        <v>15</v>
-      </c>
-      <c r="M282" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="B283" t="n">
-        <v>3.42365012991907</v>
-      </c>
-      <c r="C283" t="n">
-        <v>0.000535720394100214</v>
-      </c>
-      <c r="D283" t="n">
-        <v>0.00000032551559300092</v>
-      </c>
-      <c r="E283" t="n">
-        <v>22208.3891442413</v>
-      </c>
-      <c r="F283" t="n">
-        <v>3106197.48814528</v>
-      </c>
-      <c r="G283" t="s">
-        <v>70</v>
-      </c>
-      <c r="H283" t="n">
-        <v>2</v>
-      </c>
-      <c r="I283" t="n">
-        <v>1</v>
-      </c>
-      <c r="J283" t="s">
-        <v>14</v>
-      </c>
-      <c r="K283" t="n">
-        <v>1.708</v>
-      </c>
-      <c r="L283" t="s">
-        <v>15</v>
-      </c>
-      <c r="M283" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="1" t="n">
-        <v>45108</v>
-      </c>
-      <c r="B284" t="n">
-        <v>2.82981143638363</v>
-      </c>
-      <c r="C284" t="n">
-        <v>0.000230402550991366</v>
-      </c>
-      <c r="D284" t="n">
-        <v>0.000000185630439182017</v>
-      </c>
-      <c r="E284" t="n">
-        <v>22302.5600392389</v>
-      </c>
-      <c r="F284" t="n">
-        <v>4103901.30660954</v>
-      </c>
-      <c r="G284" t="s">
-        <v>70</v>
-      </c>
-      <c r="H284" t="n">
-        <v>0</v>
-      </c>
-      <c r="I284" t="n">
-        <v>3</v>
-      </c>
-      <c r="J284" t="s">
-        <v>14</v>
-      </c>
-      <c r="K284" t="n">
-        <v>283.981</v>
-      </c>
-      <c r="L284" t="s">
-        <v>41</v>
-      </c>
-      <c r="M284" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="B285" t="n">
-        <v>3.29773403791461</v>
-      </c>
-      <c r="C285" t="n">
-        <v>0.000450890026245706</v>
-      </c>
-      <c r="D285" t="n">
-        <v>0.000000171635779002426</v>
-      </c>
-      <c r="E285" t="n">
-        <v>19741.8358313082</v>
-      </c>
-      <c r="F285" t="n">
-        <v>9794216.18000262</v>
-      </c>
-      <c r="G285" t="s">
-        <v>70</v>
-      </c>
-      <c r="H285" t="n">
-        <v>7</v>
-      </c>
-      <c r="I285" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J285" t="s">
-        <v>69</v>
-      </c>
-      <c r="K285" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="L285" t="s">
-        <v>15</v>
-      </c>
-      <c r="M285" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="1" t="n">
-        <v>45170</v>
-      </c>
-      <c r="B286" t="n">
-        <v>2.22960962271283</v>
-      </c>
-      <c r="C286" t="n">
-        <v>0.000276353523719467</v>
-      </c>
-      <c r="D286" t="n">
-        <v>0.0000000568168052377974</v>
-      </c>
-      <c r="E286" t="n">
-        <v>22052.5520214792</v>
-      </c>
-      <c r="F286" t="n">
-        <v>6063529.62811094</v>
-      </c>
-      <c r="G286" t="s">
-        <v>70</v>
-      </c>
-      <c r="H286" t="n">
-        <v>18</v>
-      </c>
-      <c r="I286" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J286" t="s">
-        <v>69</v>
-      </c>
-      <c r="K286" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="L286" t="s">
-        <v>15</v>
-      </c>
-      <c r="M286" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="1" t="n">
-        <v>45200</v>
-      </c>
-      <c r="B287" t="n">
-        <v>3.68644563612011</v>
-      </c>
-      <c r="C287" t="n">
-        <v>0.000335359450469614</v>
-      </c>
-      <c r="D287" t="n">
-        <v>0.000000172766258933823</v>
-      </c>
-      <c r="E287" t="n">
-        <v>39964.2113872653</v>
-      </c>
-      <c r="F287" t="n">
-        <v>9467454.17764584</v>
-      </c>
-      <c r="G287" t="s">
-        <v>70</v>
-      </c>
-      <c r="H287" t="n">
-        <v>30</v>
-      </c>
-      <c r="I287" t="n">
-        <v>-26</v>
-      </c>
-      <c r="J287" t="s">
-        <v>69</v>
-      </c>
-      <c r="K287" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="L287" t="s">
-        <v>15</v>
-      </c>
-      <c r="M287" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="1" t="n">
-        <v>45231</v>
-      </c>
-      <c r="B288" t="n">
-        <v>4.77212684911462</v>
-      </c>
-      <c r="C288" t="n">
-        <v>0.000326716484116487</v>
-      </c>
-      <c r="D288" t="n">
-        <v>0.00000014970783115613</v>
-      </c>
-      <c r="E288" t="n">
-        <v>58770.9043404633</v>
-      </c>
-      <c r="F288" t="n">
-        <v>31127571.7128889</v>
-      </c>
-      <c r="G288" t="s">
-        <v>70</v>
-      </c>
-      <c r="H288" t="n">
-        <v>144</v>
-      </c>
-      <c r="I288" t="n">
-        <v>-139</v>
-      </c>
-      <c r="J288" t="s">
-        <v>69</v>
-      </c>
-      <c r="K288" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="L288" t="s">
-        <v>15</v>
-      </c>
-      <c r="M288" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="1" t="n">
-        <v>45261</v>
-      </c>
-      <c r="B289" t="n">
-        <v>4.41802680743615</v>
-      </c>
-      <c r="C289" t="n">
-        <v>0.000224919003733297</v>
-      </c>
-      <c r="D289" t="n">
-        <v>0.000000109806298304843</v>
-      </c>
-      <c r="E289" t="n">
-        <v>52002.1028470801</v>
-      </c>
-      <c r="F289" t="n">
-        <v>42495051.4308242</v>
-      </c>
-      <c r="G289" t="s">
-        <v>70</v>
-      </c>
-      <c r="H289" t="n">
-        <v>187</v>
-      </c>
-      <c r="I289" t="n">
-        <v>-183</v>
-      </c>
-      <c r="J289" t="s">
-        <v>69</v>
-      </c>
-      <c r="K289" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="L289" t="s">
-        <v>15</v>
-      </c>
-      <c r="M289" t="s">
-        <v>64</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
